--- a/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>FND</t>
   </si>
@@ -656,415 +656,427 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45288</v>
+      </c>
+      <c r="E7" s="2">
         <v>45197</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45106</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45015</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44924</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44833</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44560</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44378</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44287</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44098</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44007</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43916</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43825</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43734</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43643</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43552</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43461</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43370</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43279</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43188</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43097</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43006</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42915</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42824</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42733</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1048100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1107800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1135900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1122100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1048100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1097800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1089800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1028700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>914300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>876600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>860100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>782500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>723700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>684800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>462400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>554900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>527000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>521100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>520300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>477100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>436700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>435900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>434300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>402900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>389500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>343900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>344000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>307300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>278300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>271300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>606000</v>
+      </c>
+      <c r="E9" s="3">
         <v>640400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>656300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>652900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>612200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>650300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>653600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>620700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>559700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>511200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>494700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>445600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>416100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>390200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>265700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>318900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>297000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>307300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>302500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>275700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>255700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>257700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>256600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>237600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>227100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>201400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>201800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>181800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>163500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>160300</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>442100</v>
+      </c>
+      <c r="E10" s="3">
         <v>467400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>479600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>469200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>435900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>447500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>436200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>408000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>354600</v>
-      </c>
-      <c r="L10" s="3">
-        <v>365400</v>
       </c>
       <c r="M10" s="3">
         <v>365400</v>
       </c>
       <c r="N10" s="3">
+        <v>365400</v>
+      </c>
+      <c r="O10" s="3">
         <v>336900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>307600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>294600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>196700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>236000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>230000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>213800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>217800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>201400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>181000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>178200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>177700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>165300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>162400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>142500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>142200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>125500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>114800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1097,8 +1109,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1189,8 +1202,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,25 +1297,28 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1307,35 +1326,35 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>1700</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-1000</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1343,8 +1362,8 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1352,29 +1371,32 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>5400</v>
       </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1465,8 +1487,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1496,192 +1521,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1002000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1023000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1040900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1026500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>953300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>996200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>983400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>934800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>853200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>793200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>763300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>686600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>655600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>606000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>440200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>508300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>484900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>489700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>474400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>437300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>413400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>401600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>397000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>366400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>357100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>315300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>315400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>284600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>260000</v>
       </c>
-      <c r="AF17" s="3" t="s">
+      <c r="AG17" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E18" s="3">
         <v>84800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>95000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>95600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>94800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>101600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>106400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>93900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>61100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>83400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>96800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>95900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>68100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>78800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>22200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>46600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>42100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>31400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>45900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>39800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>23300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>34300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>37300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>36500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>32400</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>28600</v>
       </c>
       <c r="AC18" s="3">
         <v>28600</v>
       </c>
       <c r="AD18" s="3">
+        <v>28600</v>
+      </c>
+      <c r="AE18" s="3">
         <v>22700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>18300</v>
       </c>
-      <c r="AF18" s="3" t="s">
+      <c r="AG18" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,8 +1746,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1747,11 +1780,11 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1774,11 +1807,11 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1803,379 +1836,394 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-      <c r="AF20" s="3" t="s">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>101100</v>
+      </c>
+      <c r="E21" s="3">
         <v>135700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>144700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>141900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>137100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>141800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>144400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>128600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>94800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>113800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>125400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>122400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>92400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>101700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>44400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>68800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>62800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>49800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>63600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>56900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>38300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>47600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>49300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>48000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>42800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>38200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>37800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>31600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>26600</v>
       </c>
-      <c r="AF21" s="3" t="s">
+      <c r="AG21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>900</v>
+      </c>
+      <c r="E22" s="3">
         <v>1200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1200</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1100</v>
       </c>
       <c r="L22" s="3">
         <v>1100</v>
       </c>
       <c r="M22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>3400</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>5400</v>
       </c>
       <c r="AE22" s="3">
         <v>5400</v>
       </c>
       <c r="AF22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AG22" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E23" s="3">
         <v>83500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>92100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>90700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>89400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>98600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>104700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>92800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>60000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>82300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>97300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>94600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>65800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>76800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>19800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>44900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>40400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>29400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>43700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>36800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>20500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>32100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>35100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>34700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>30000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>26000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>25300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>17300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>12900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E24" s="3">
         <v>17600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>20600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>19100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>20200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>22500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>22900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>21900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>18800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-12200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-11600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2266,192 +2314,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E26" s="3">
         <v>65900</v>
-      </c>
-      <c r="E26" s="3">
-        <v>71500</v>
       </c>
       <c r="F26" s="3">
         <v>71500</v>
       </c>
       <c r="G26" s="3">
+        <v>71500</v>
+      </c>
+      <c r="H26" s="3">
         <v>69200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>76200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>81800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>71000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>49900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>74600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>82900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>75800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>57100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>68800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>32000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>37100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>35300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>41000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>43600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>30700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>17300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>26000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>39800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>31900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>30100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>23300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>20400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>11100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>16700</v>
       </c>
-      <c r="AF26" s="3" t="s">
+      <c r="AG26" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E27" s="3">
         <v>65900</v>
-      </c>
-      <c r="E27" s="3">
-        <v>71500</v>
       </c>
       <c r="F27" s="3">
         <v>71500</v>
       </c>
       <c r="G27" s="3">
+        <v>71500</v>
+      </c>
+      <c r="H27" s="3">
         <v>69200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>76200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>81800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>71000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>49900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>74600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>82900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>75800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>57100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>68800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>32000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>37100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>35300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>41000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>43600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>30700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>17300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>26000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>39800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>31900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>30100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>23300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>20400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>11100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>16700</v>
       </c>
-      <c r="AF27" s="3" t="s">
+      <c r="AG27" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2542,8 +2599,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2586,17 +2646,17 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3" t="s">
+      <c r="S29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2604,23 +2664,23 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>600</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X29" s="3">
         <v>600</v>
       </c>
       <c r="Y29" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>17800</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2634,8 +2694,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2726,8 +2789,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2818,8 +2884,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2851,11 +2920,11 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2878,11 +2947,11 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -2907,103 +2976,109 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-      <c r="AF32" s="3" t="s">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E33" s="3">
         <v>65900</v>
-      </c>
-      <c r="E33" s="3">
-        <v>71500</v>
       </c>
       <c r="F33" s="3">
         <v>71500</v>
       </c>
       <c r="G33" s="3">
+        <v>71500</v>
+      </c>
+      <c r="H33" s="3">
         <v>69200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>76200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>81800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>71000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>49900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>74600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>82900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>75800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>57100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>68800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>32000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>37100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>35300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>41000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>43600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>30700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>17900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>26600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>39800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>31900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>48000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>23300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>20400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>11100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>16700</v>
       </c>
-      <c r="AF33" s="3" t="s">
+      <c r="AG33" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3094,197 +3169,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E35" s="3">
         <v>65900</v>
-      </c>
-      <c r="E35" s="3">
-        <v>71500</v>
       </c>
       <c r="F35" s="3">
         <v>71500</v>
       </c>
       <c r="G35" s="3">
+        <v>71500</v>
+      </c>
+      <c r="H35" s="3">
         <v>69200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>76200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>81800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>71000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>49900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>74600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>82900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>75800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>57100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>68800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>32000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>37100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>35300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>41000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>43600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>30700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>17900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>26600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>39800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>31900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>48000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>23300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>20400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>11100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>16700</v>
       </c>
-      <c r="AF35" s="3" t="s">
+      <c r="AG35" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45288</v>
+      </c>
+      <c r="E38" s="2">
         <v>45197</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45106</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45015</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44924</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44833</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44560</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44378</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44287</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44098</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44007</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43916</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43825</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43734</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43643</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43552</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43461</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43370</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43279</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43188</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43097</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43006</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42915</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42824</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42733</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3317,8 +3401,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,79 +3436,80 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E41" s="3">
         <v>61600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>31800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>139400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>330100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>366100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>354100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>307800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>271100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>134400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>289900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>27000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>84100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>51500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>600</v>
-      </c>
-      <c r="X41" s="3">
-        <v>500</v>
       </c>
       <c r="Y41" s="3">
         <v>500</v>
       </c>
       <c r="Z41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AA41" s="3">
         <v>600</v>
@@ -3432,19 +3518,22 @@
         <v>600</v>
       </c>
       <c r="AC41" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AD41" s="3">
         <v>400</v>
       </c>
       <c r="AE41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF41" s="3">
         <v>500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3535,376 +3624,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>127400</v>
+      </c>
+      <c r="E43" s="3">
         <v>113900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>102300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>88000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>102100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>112400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>111700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>97800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>85000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>81500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>72800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>60000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>50400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>81000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>82100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>50600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>72200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>54500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>38500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>66100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>71900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>65900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>57200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>48000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>66500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>52600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>40600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>33400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>34500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>34800</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1106200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1105500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1172500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1181100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1292300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1320500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1344100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1149500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1008200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>833100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>683800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>607600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>654000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>598500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>594300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>588900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>581900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>484000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>446400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>437500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>471000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>403800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>432400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>426700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>428000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>395600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>367500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>316500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>293700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>301600</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E45" s="3">
         <v>55100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>56600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>54300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>53300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>56500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>49300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>43400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>40800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>49500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>42700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>40200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>28300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>19200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>21600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>20400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>21100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>27700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>23300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>15900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>16600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>12100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>11100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>9500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1316600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1336100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1335500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1328500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1457500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1497100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1511300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1322500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1273300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1294200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1165400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1061900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1040500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>974000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>830000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>951000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>701500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>643700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>564000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>527400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>559500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>486800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>502300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>486400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>503200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>456300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>416100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>359900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>336200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>343800</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3995,135 +4099,141 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2912500</v>
+      </c>
+      <c r="E48" s="3">
         <v>2869100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2701200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2576500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2463700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2321500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2263500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2144500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2032800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1918300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1782400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1558800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1495700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1396900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1354900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1338600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1278500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1169000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1102700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>998000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>328400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>300300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>271500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>245400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>221000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>200400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>183600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>163800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>150500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>135500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>411800</v>
+      </c>
+      <c r="E49" s="3">
         <v>412700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>414600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>407100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>407800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>406300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>407100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>407300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>407400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>408200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>408900</v>
-      </c>
-      <c r="N49" s="3">
-        <v>336700</v>
       </c>
       <c r="O49" s="3">
         <v>336700</v>
@@ -4141,7 +4251,7 @@
         <v>336700</v>
       </c>
       <c r="T49" s="3">
-        <v>336800</v>
+        <v>336700</v>
       </c>
       <c r="U49" s="3">
         <v>336800</v>
@@ -4179,8 +4289,11 @@
       <c r="AF49" s="3">
         <v>336800</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>336800</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4271,8 +4384,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4363,100 +4479,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E52" s="3">
         <v>20200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>24200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>23200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>22200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4547,100 +4669,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4662600</v>
+      </c>
+      <c r="E54" s="3">
         <v>4638100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4475500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4335200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4351200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4244700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4199400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3893400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3730700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3628100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3364300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2964700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2880400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2714400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2528700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2633900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2324300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2156900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2011100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1873400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1234100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1131900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1118400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1075900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1068000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1000900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>944200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>868400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>831200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>820400</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +4801,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4707,100 +4836,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>679300</v>
+      </c>
+      <c r="E57" s="3">
         <v>706300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>664700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>572500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>590900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>642100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>770200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>688500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>661900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>634300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>529200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>402100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>417900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>362500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>326000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>319800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>368500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>318400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>272700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>229500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>313500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>237800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>265000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>255000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>258700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>249200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>243600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>205900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>158500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>165800</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4820,43 +4953,43 @@
         <v>2100</v>
       </c>
       <c r="I58" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="J58" s="3">
         <v>1600</v>
       </c>
       <c r="K58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L58" s="3">
         <v>2100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1800</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
       <c r="U58" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="V58" s="3">
         <v>3500</v>
@@ -4889,378 +5022,393 @@
         <v>3500</v>
       </c>
       <c r="AF58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AG58" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>470600</v>
+      </c>
+      <c r="E59" s="3">
         <v>466000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>449400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>432000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>413800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>417200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>425500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>403300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>368000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>376100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>325500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>268700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>279300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>253700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>205100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>184900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>184100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>174100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>148400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>165400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>87300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>82900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>66800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>72600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>97100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>91500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>75300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>83800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>81700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1152000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1174400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1116200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1006500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1006800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1061400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1197300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1093300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1032000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1012000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>860200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>673000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>698800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>618900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>533700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>506500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>552500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>492400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>424600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>398300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>404300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>324200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>335300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>331100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>359300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>344200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>322400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>293200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>243700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>194900</v>
+      </c>
+      <c r="E61" s="3">
         <v>195000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>230100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>301700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>405600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>371900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>264200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>195700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>195800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>195900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>195400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>195500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>207200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>206800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>207000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>413300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>142600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>143300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>140500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>143300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>141800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>142500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>156800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>169800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>185600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>183900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>178300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>351200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>387200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>157600</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1384600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1383200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1319400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1298500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1281800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1228800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1243700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1202000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1179700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1155300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1129000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1015500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>977000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>957200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>937600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>904800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>864800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>798100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>775100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>711800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>103700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>101500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>91600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>87400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>80300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>84600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>82300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>77800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>65900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5351,8 +5499,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5443,8 +5594,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5535,100 +5689,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2731600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2752600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2665700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2606800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2694100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2662000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2705100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2491000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2407500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2363200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2184700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1884000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1883000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1782900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1678200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1824600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1560000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1433800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1340200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1253400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>649800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>568200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>583700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>588300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>625100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>612800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>583100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>722200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>696900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>479100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5661,8 +5821,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5753,8 +5914,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5845,8 +6009,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5937,8 +6104,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6029,100 +6199,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1416400</v>
+      </c>
+      <c r="E72" s="3">
         <v>1379300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1313400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1241900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1170400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1101200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1025000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>943200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>872200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>822400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>747700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>664800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>589000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>531900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>463100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>431100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>394000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>358700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>317700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>274100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>243600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>225700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>199100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>159200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>119600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>71600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>48300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>27900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>16800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6213,8 +6389,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6305,8 +6484,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6397,100 +6579,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1931000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1885500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1809800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1728400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1657200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1582600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1494300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1402400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1323200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1264900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1179600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1080700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>997400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>931500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>850500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>809300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>764300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>723000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>670900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>620000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>584300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>563700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>534700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>487600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>442900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>388200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>361100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>146100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>134300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>341400</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6581,197 +6769,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45288</v>
+      </c>
+      <c r="E80" s="2">
         <v>45197</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45106</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45015</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44924</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44833</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44560</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44378</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44287</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44098</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44007</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43916</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43825</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43734</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43643</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43552</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43461</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43370</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43279</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43188</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43097</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43006</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42915</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42824</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42733</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E81" s="3">
         <v>65900</v>
-      </c>
-      <c r="E81" s="3">
-        <v>71500</v>
       </c>
       <c r="F81" s="3">
         <v>71500</v>
       </c>
       <c r="G81" s="3">
+        <v>71500</v>
+      </c>
+      <c r="H81" s="3">
         <v>69200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>76200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>81800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>71000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>49900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>74600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>82900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>75800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>57100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>68800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>32000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>37100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>35300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>41000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>43600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>30700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>17900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>26600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>39800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>31900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>48000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>23300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>20400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>11100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>16700</v>
       </c>
-      <c r="AF81" s="3" t="s">
+      <c r="AG81" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6804,100 +7001,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E83" s="3">
         <v>50900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>49700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>46400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>42300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>40100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>38000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>33700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>30400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>27700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>26400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>24400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>22900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>22300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>22100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>20700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>18400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>17700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>17200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>14900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>13400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>11500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>10400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>9600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>9100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>8900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>8300</v>
       </c>
-      <c r="AF83" s="3" t="s">
+      <c r="AG83" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6988,8 +7189,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7080,8 +7284,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7172,8 +7379,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7264,8 +7474,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7356,100 +7569,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>104600</v>
+      </c>
+      <c r="E89" s="3">
         <v>222300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>226400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>250300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>105100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-63600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>108300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>155600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>101000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>136500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>173000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>72000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>24700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>87400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>95100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>27000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>41900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>59800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>43300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>40600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>26300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>16400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>10400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>56100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>18500</v>
       </c>
-      <c r="AF89" s="3" t="s">
+      <c r="AG89" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7482,100 +7701,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-133900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-134500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-139800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-139400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-133800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-108500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-113400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-130000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-145600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-86200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-45900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-102800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-43700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-27600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-38400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-55000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-62800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-46500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-31600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-42000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-46000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-35600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-27800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-24100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-19800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AF91" s="3" t="s">
+      <c r="AG91" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7666,8 +7889,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,100 +7984,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-133900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-134700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-156900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-139400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-136500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-108500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-109200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-101400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-130000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-145800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-149600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-45900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-102800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-43700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-27600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-38400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-55000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-62800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-46500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-31600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-42000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-46000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-35600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-27800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-32600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-25700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-22400</v>
       </c>
-      <c r="AF94" s="3" t="s">
+      <c r="AG94" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7884,8 +8116,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7976,8 +8209,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8068,8 +8304,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8160,8 +8399,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8252,100 +8494,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-30100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-70300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-115600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>33400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>110600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>72400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>7400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-199900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>276600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>8100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-13800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>6300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>7900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>15300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-36300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>4000</v>
       </c>
-      <c r="AF100" s="3" t="s">
+      <c r="AG100" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8436,74 +8684,77 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E102" s="3">
         <v>57500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-25700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-107600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-190600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-36000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>12000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>46300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>36600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>136700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-155500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>262900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-57100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>32700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>51000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>100</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
         <v>0</v>
       </c>
@@ -8514,18 +8765,21 @@
         <v>0</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>100</v>
       </c>
-      <c r="AF102" s="3" t="s">
+      <c r="AG102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>FND</t>
   </si>
@@ -656,427 +656,440 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45379</v>
+      </c>
+      <c r="E7" s="2">
         <v>45288</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45197</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45106</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45015</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44924</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44833</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44560</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44378</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44287</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44098</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44007</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43916</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43825</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43734</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43643</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43552</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43461</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43370</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43279</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43188</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43097</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43006</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42915</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42824</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42733</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1097300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1048100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1107800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1135900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1122100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1048100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1097800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1089800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1028700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>914300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>876600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>860100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>782500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>723700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>684800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>462400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>554900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>527000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>521100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>520300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>477100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>436700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>435900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>434300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>402900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>389500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>343900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>344000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>307300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>278300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>271300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>627300</v>
+      </c>
+      <c r="E9" s="3">
         <v>606000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>640400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>656300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>652900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>612200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>650300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>653600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>620700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>559700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>511200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>494700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>445600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>416100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>390200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>265700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>318900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>297000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>307300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>302500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>275700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>255700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>257700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>256600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>237600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>227100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>201400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>201800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>181800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>163500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>160300</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>470000</v>
+      </c>
+      <c r="E10" s="3">
         <v>442100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>467400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>479600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>469200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>435900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>447500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>436200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>408000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>354600</v>
-      </c>
-      <c r="M10" s="3">
-        <v>365400</v>
       </c>
       <c r="N10" s="3">
         <v>365400</v>
       </c>
       <c r="O10" s="3">
+        <v>365400</v>
+      </c>
+      <c r="P10" s="3">
         <v>336900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>307600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>294600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>196700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>236000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>230000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>213800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>217800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>201400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>181000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>178200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>177700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>165300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>162400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>142500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>142200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>125500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>114800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1110,8 +1123,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1205,8 +1219,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1300,28 +1317,31 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>900</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1329,35 +1349,35 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1700</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-1000</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1365,8 +1385,8 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1374,29 +1394,32 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>5400</v>
       </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1490,8 +1513,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1522,198 +1548,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1038000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1002000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1023000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1040900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1026500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>953300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>996200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>983400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>934800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>853200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>793200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>763300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>686600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>655600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>606000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>440200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>508300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>484900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>489700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>474400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>437300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>413400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>401600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>397000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>366400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>357100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>315300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>315400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>284600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>260000</v>
       </c>
-      <c r="AG17" s="3" t="s">
+      <c r="AH17" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E18" s="3">
         <v>46100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>84800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>95000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>95600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>94800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>101600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>106400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>93900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>61100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>83400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>96800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>95900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>68100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>78800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>22200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>46600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>42100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>31400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>45900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>39800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>23300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>34300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>37300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>36500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>32400</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>28600</v>
       </c>
       <c r="AD18" s="3">
         <v>28600</v>
       </c>
       <c r="AE18" s="3">
+        <v>28600</v>
+      </c>
+      <c r="AF18" s="3">
         <v>22700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>18300</v>
       </c>
-      <c r="AG18" s="3" t="s">
+      <c r="AH18" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1747,8 +1780,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1783,11 +1817,11 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1810,11 +1844,11 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -1839,391 +1873,406 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-      <c r="AG20" s="3" t="s">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>115700</v>
+      </c>
+      <c r="E21" s="3">
         <v>101100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>135700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>144700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>141900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>137100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>141800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>144400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>128600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>94800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>113800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>125400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>122400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>92400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>101700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>44400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>68800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>62800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>49800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>63600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>56900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>38300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>47600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>49300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>48000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>42800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>38200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>37800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>31600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>26600</v>
       </c>
-      <c r="AG21" s="3" t="s">
+      <c r="AH21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E22" s="3">
         <v>900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1200</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1100</v>
       </c>
       <c r="M22" s="3">
         <v>1100</v>
       </c>
       <c r="N22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O22" s="3">
         <v>400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3400</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>5400</v>
       </c>
       <c r="AF22" s="3">
         <v>5400</v>
       </c>
       <c r="AG22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AH22" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E23" s="3">
         <v>45300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>83500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>92100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>90700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>89400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>98600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>104700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>92800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>60000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>82300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>97300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>94600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>65800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>76800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>19800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>44900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>40400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>29400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>43700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>36800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>20500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>32100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>35100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>34700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>30000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>26000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>25300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>17300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>12900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E24" s="3">
         <v>8200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>17600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>20600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>19100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>20200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>22500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>22900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>18800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-12200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-11600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2317,198 +2366,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E26" s="3">
         <v>37100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>65900</v>
-      </c>
-      <c r="F26" s="3">
-        <v>71500</v>
       </c>
       <c r="G26" s="3">
         <v>71500</v>
       </c>
       <c r="H26" s="3">
+        <v>71500</v>
+      </c>
+      <c r="I26" s="3">
         <v>69200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>76200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>81800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>71000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>49900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>74600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>82900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>75800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>57100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>68800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>32000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>37100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>35300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>41000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>43600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>30700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>17300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>26000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>39800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>31900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>30100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>23300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>20400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>11100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>16700</v>
       </c>
-      <c r="AG26" s="3" t="s">
+      <c r="AH26" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E27" s="3">
         <v>37100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>65900</v>
-      </c>
-      <c r="F27" s="3">
-        <v>71500</v>
       </c>
       <c r="G27" s="3">
         <v>71500</v>
       </c>
       <c r="H27" s="3">
+        <v>71500</v>
+      </c>
+      <c r="I27" s="3">
         <v>69200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>76200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>81800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>71000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>49900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>74600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>82900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>75800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>57100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>68800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>32000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>37100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>35300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>41000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>43600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>30700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>17300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>26000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>39800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>31900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>30100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>23300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>20400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>11100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>16700</v>
       </c>
-      <c r="AG27" s="3" t="s">
+      <c r="AH27" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2602,8 +2660,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2649,17 +2710,17 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3" t="s">
+      <c r="T29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2667,23 +2728,23 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>600</v>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y29" s="3">
         <v>600</v>
       </c>
       <c r="Z29" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>17800</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2697,8 +2758,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2792,8 +2856,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2887,8 +2954,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2923,11 +2993,11 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2950,11 +3020,11 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -2979,106 +3049,112 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-      <c r="AG32" s="3" t="s">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E33" s="3">
         <v>37100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>65900</v>
-      </c>
-      <c r="F33" s="3">
-        <v>71500</v>
       </c>
       <c r="G33" s="3">
         <v>71500</v>
       </c>
       <c r="H33" s="3">
+        <v>71500</v>
+      </c>
+      <c r="I33" s="3">
         <v>69200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>76200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>81800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>71000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>49900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>74600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>82900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>75800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>57100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>68800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>32000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>37100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>41000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>43600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>30700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>17900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>26600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>39800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>31900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>48000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>23300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>20400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>11100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>16700</v>
       </c>
-      <c r="AG33" s="3" t="s">
+      <c r="AH33" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3172,203 +3248,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E35" s="3">
         <v>37100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>65900</v>
-      </c>
-      <c r="F35" s="3">
-        <v>71500</v>
       </c>
       <c r="G35" s="3">
         <v>71500</v>
       </c>
       <c r="H35" s="3">
+        <v>71500</v>
+      </c>
+      <c r="I35" s="3">
         <v>69200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>76200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>81800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>71000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>49900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>74600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>82900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>75800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>57100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>68800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>32000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>37100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>41000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>43600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>30700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>17900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>26600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>39800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>31900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>48000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>23300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>20400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>11100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>16700</v>
       </c>
-      <c r="AG35" s="3" t="s">
+      <c r="AH35" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45379</v>
+      </c>
+      <c r="E38" s="2">
         <v>45288</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45197</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45106</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45015</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44924</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44833</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44560</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44378</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44287</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44098</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44007</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43916</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43825</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43734</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43643</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43552</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43461</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43370</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43279</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43188</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43097</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43006</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42915</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42824</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42733</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3402,8 +3487,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3437,82 +3523,83 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E41" s="3">
         <v>34400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>61600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>31800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>139400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>330100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>366100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>354100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>307800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>271100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>134400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>289900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>27000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>84100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>51500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>600</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>500</v>
       </c>
       <c r="Z41" s="3">
         <v>500</v>
       </c>
       <c r="AA41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AB41" s="3">
         <v>600</v>
@@ -3521,19 +3608,22 @@
         <v>600</v>
       </c>
       <c r="AD41" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AE41" s="3">
         <v>400</v>
       </c>
       <c r="AF41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG41" s="3">
         <v>500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3627,388 +3717,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>116800</v>
+      </c>
+      <c r="E43" s="3">
         <v>127400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>113900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>102300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>88000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>102100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>112400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>111700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>97800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>85000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>81500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>72800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>60000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>50400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>81000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>82100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>50600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>72200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>54500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>38500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>66100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>71900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>65900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>57200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>48000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>66500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>52600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>40600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>33400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>34500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>34800</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1032100</v>
+      </c>
+      <c r="E44" s="3">
         <v>1106200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1105500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1172500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1181100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1292300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1320500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1344100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1149500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1008200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>833100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>683800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>607600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>654000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>598500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>594300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>588900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>581900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>484000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>446400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>437500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>471000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>403800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>432400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>426700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>428000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>395600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>367500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>316500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>293700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>301600</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E45" s="3">
         <v>48700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>55100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>56600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>54300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>53300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>56500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>49300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>43400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>40800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>49500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>42700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>40200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>19200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>21600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>20400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>21100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>27700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>23300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>15900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>16600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>12100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>11100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>8200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>9500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>7500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1256100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1316600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1336100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1335500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1328500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1457500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1497100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1511300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1322500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1273300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1294200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1165400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1061900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1040500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>974000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>830000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>951000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>701500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>643700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>564000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>527400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>559500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>486800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>502300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>486400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>503200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>456300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>416100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>359900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>336200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>343800</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4102,141 +4207,147 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2969100</v>
+      </c>
+      <c r="E48" s="3">
         <v>2912500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2869100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2701200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2576500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2463700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2321500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2263500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2144500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2032800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1918300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1782400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1558800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1495700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1396900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1354900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1338600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1278500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1169000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1102700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>998000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>328400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>300300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>271500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>245400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>221000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>200400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>183600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>163800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>150500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>135500</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>410900</v>
+      </c>
+      <c r="E49" s="3">
         <v>411800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>412700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>414600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>407100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>407800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>406300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>407100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>407300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>407400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>408200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>408900</v>
-      </c>
-      <c r="O49" s="3">
-        <v>336700</v>
       </c>
       <c r="P49" s="3">
         <v>336700</v>
@@ -4254,7 +4365,7 @@
         <v>336700</v>
       </c>
       <c r="U49" s="3">
-        <v>336800</v>
+        <v>336700</v>
       </c>
       <c r="V49" s="3">
         <v>336800</v>
@@ -4292,8 +4403,11 @@
       <c r="AG49" s="3">
         <v>336800</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>336800</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4387,8 +4501,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4482,103 +4599,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E52" s="3">
         <v>21600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>20200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>24200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>23200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>22200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>17600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4672,103 +4795,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4658700</v>
+      </c>
+      <c r="E54" s="3">
         <v>4662600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4638100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4475500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4335200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4351200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4244700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4199400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3893400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3730700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3628100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3364300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2964700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2880400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2714400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2528700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2633900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2324300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2156900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2011100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1873400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1234100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1131900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1118400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1075900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1068000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1000900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>944200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>868400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>831200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>820400</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4802,8 +4931,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4837,103 +4967,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>641200</v>
+      </c>
+      <c r="E57" s="3">
         <v>679300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>706300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>664700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>572500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>590900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>642100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>770200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>688500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>661900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>634300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>529200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>402100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>417900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>362500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>326000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>319800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>368500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>318400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>272700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>229500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>313500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>237800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>265000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>255000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>258700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>249200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>243600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>205900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>158500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>165800</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4956,43 +5090,43 @@
         <v>2100</v>
       </c>
       <c r="J58" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="K58" s="3">
         <v>1600</v>
       </c>
       <c r="L58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M58" s="3">
         <v>2100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1800</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
       <c r="V58" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="W58" s="3">
         <v>3500</v>
@@ -5025,390 +5159,405 @@
         <v>3500</v>
       </c>
       <c r="AG58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AH58" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>430400</v>
+      </c>
+      <c r="E59" s="3">
         <v>470600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>466000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>449400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>432000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>413800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>417200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>425500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>403300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>368000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>376100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>325500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>268700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>279300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>253700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>205100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>184900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>184100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>174100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>148400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>165400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>87300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>82900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>66800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>72600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>97100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>91500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>75300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>83800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>81700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1073600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1152000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1174400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1116200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1006500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1006800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1061400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1197300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1093300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1032000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1012000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>860200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>673000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>698800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>618900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>533700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>506500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>552500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>492400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>424600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>398300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>404300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>324200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>335300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>331100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>359300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>344200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>322400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>293200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>243700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>194800</v>
+      </c>
+      <c r="E61" s="3">
         <v>194900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>195000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>230100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>301700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>405600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>371900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>264200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>195700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>195800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>195900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>195400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>195500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>207200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>206800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>207000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>413300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>142600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>143300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>140500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>143300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>141800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>142500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>156800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>169800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>185600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>183900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>178300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>351200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>387200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>157600</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1409400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1384600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1383200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1319400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1298500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1281800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1228800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1243700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1202000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1179700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1155300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1129000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1015500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>977000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>957200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>937600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>904800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>864800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>798100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>775100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>711800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>103700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>101500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>91600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>87400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>80300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>84600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>82300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>77800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>65900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5502,8 +5651,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5597,8 +5749,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5692,103 +5847,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2677900</v>
+      </c>
+      <c r="E66" s="3">
         <v>2731600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2752600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2665700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2606800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2694100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2662000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2705100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2491000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2407500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2363200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2184700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1884000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1883000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1782900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1678200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1824600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1560000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1433800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1340200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1253400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>649800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>568200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>583700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>588300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>625100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>612800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>583100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>722200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>696900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>479100</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5822,8 +5983,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5917,8 +6079,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6012,8 +6177,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6107,8 +6275,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6202,103 +6373,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1466400</v>
+      </c>
+      <c r="E72" s="3">
         <v>1416400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1379300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1313400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1241900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1170400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1101200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1025000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>943200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>872200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>822400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>747700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>664800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>589000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>531900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>463100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>431100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>394000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>358700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>317700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>274100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>243600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>225700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>199100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>159200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>119600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>71600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>48300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>27900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>16800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6392,8 +6569,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6487,8 +6667,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6582,103 +6765,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1980800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1931000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1885500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1809800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1728400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1657200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1582600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1494300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1402400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1323200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1264900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1179600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1080700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>997400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>931500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>850500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>809300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>764300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>723000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>670900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>620000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>584300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>563700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>534700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>487600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>442900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>388200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>361100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>146100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>134300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>341400</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6772,203 +6961,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45379</v>
+      </c>
+      <c r="E80" s="2">
         <v>45288</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45197</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45106</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45015</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44924</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44833</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44560</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44378</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44287</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44098</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44007</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43916</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43825</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43734</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43643</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43552</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43461</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43370</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43279</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43188</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43097</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43006</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42915</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42824</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42733</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E81" s="3">
         <v>37100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>65900</v>
-      </c>
-      <c r="F81" s="3">
-        <v>71500</v>
       </c>
       <c r="G81" s="3">
         <v>71500</v>
       </c>
       <c r="H81" s="3">
+        <v>71500</v>
+      </c>
+      <c r="I81" s="3">
         <v>69200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>76200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>81800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>71000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>49900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>74600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>82900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>75800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>57100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>68800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>32000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>37100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>41000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>43600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>30700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>17900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>26600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>39800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>31900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>48000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>23300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>20400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>11100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>16700</v>
       </c>
-      <c r="AG81" s="3" t="s">
+      <c r="AH81" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7002,103 +7200,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E83" s="3">
         <v>54900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>50900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>49700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>46400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>42300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>40100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>38000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>34600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>33700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>30400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>27700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>26400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>24400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>22900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>22300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>22100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>20700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>18400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>17700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>17200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>14900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>13400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>11500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>10400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>9600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>9100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>8900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>8300</v>
       </c>
-      <c r="AG83" s="3" t="s">
+      <c r="AH83" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7192,8 +7394,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7287,8 +7492,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7382,8 +7590,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7477,8 +7688,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7572,103 +7786,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>147500</v>
+      </c>
+      <c r="E89" s="3">
         <v>104600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>222300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>226400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>250300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>105100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-63600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>108300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>155600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>101000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>136500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>173000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>72000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>24700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>87400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>95100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>27000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>41900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>59800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>43300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>40600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>26300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>16400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>10400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>56100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>18500</v>
       </c>
-      <c r="AG89" s="3" t="s">
+      <c r="AH89" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7702,103 +7922,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-111700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-133900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-134500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-139800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-139400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-133800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-108500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-113400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-130000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-145600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-86200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-45900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-102800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-43700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-27600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-38400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-55000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-62800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-46500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-31600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-46000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-35600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-27800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-24100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-19800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AG91" s="3" t="s">
+      <c r="AH91" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7892,8 +8116,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7987,103 +8214,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-111700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-133900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-134700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-156900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-139400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-136500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-108500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-109200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-101400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-130000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-145800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-149600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-45900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-102800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-43700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-27600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-38400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-55000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-62800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-46500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-31600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-46000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-27800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-32600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-25700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-22400</v>
       </c>
-      <c r="AG94" s="3" t="s">
+      <c r="AH94" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8117,8 +8350,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8212,8 +8446,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8307,8 +8544,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8402,8 +8642,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8497,103 +8740,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E100" s="3">
         <v>2000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-30100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-70300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-115600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>33400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>110600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>72400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>6000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-8800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>7400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-199900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>276600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>8100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-13800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>6300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>7900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>15300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-36300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>4000</v>
       </c>
-      <c r="AG100" s="3" t="s">
+      <c r="AH100" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8687,77 +8936,80 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-27200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>57500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-25700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-107600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-190600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-36000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>12000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>46300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>36600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>136700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-155500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>262900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-57100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>32700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>51000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>100</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
         <v>0</v>
       </c>
@@ -8768,18 +9020,21 @@
         <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-100</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>100</v>
       </c>
-      <c r="AG102" s="3" t="s">
+      <c r="AH102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>FND</t>
   </si>
@@ -656,440 +656,453 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45470</v>
+      </c>
+      <c r="E7" s="2">
         <v>45379</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45288</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45197</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45106</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45015</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44924</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44833</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44560</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44378</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44287</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44098</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44007</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43916</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43825</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43734</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43643</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43552</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43461</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43370</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43279</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43188</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43097</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43006</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42915</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42824</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42733</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1133100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1097300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1048100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1107800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1135900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1122100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1048100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1097800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1089800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1028700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>914300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>876600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>860100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>782500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>723700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>684800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>462400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>554900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>527000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>521100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>520300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>477100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>436700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>435900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>434300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>402900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>389500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>343900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>344000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>307300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>278300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>271300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>642100</v>
+      </c>
+      <c r="E9" s="3">
         <v>627300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>606000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>640400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>656300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>652900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>612200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>650300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>653600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>620700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>559700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>511200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>494700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>445600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>416100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>390200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>265700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>318900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>297000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>307300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>302500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>275700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>255700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>257700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>256600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>237600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>227100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>201400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>201800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>181800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>163500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>160300</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>491000</v>
+      </c>
+      <c r="E10" s="3">
         <v>470000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>442100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>467400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>479600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>469200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>435900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>447500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>436200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>408000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>354600</v>
-      </c>
-      <c r="N10" s="3">
-        <v>365400</v>
       </c>
       <c r="O10" s="3">
         <v>365400</v>
       </c>
       <c r="P10" s="3">
+        <v>365400</v>
+      </c>
+      <c r="Q10" s="3">
         <v>336900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>307600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>294600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>196700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>236000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>230000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>213800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>217800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>201400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>181000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>178200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>177700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>165300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>162400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>142500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>142200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>125500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>114800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1124,8 +1137,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1222,8 +1236,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1320,31 +1337,34 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1352,35 +1372,35 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1700</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-1000</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1388,8 +1408,8 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1397,29 +1417,32 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>5400</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1516,8 +1539,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1549,204 +1575,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1061800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1038000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1002000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1023000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1040900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1026500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>953300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>996200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>983400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>934800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>853200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>793200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>763300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>686600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>655600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>606000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>440200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>508300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>484900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>489700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>474400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>437300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>413400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>401600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>397000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>366400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>357100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>315300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>315400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>284600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>260000</v>
       </c>
-      <c r="AH17" s="3" t="s">
+      <c r="AI17" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>71300</v>
+      </c>
+      <c r="E18" s="3">
         <v>59300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>46100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>84800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>95000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>95600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>94800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>101600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>106400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>93900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>61100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>83400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>96800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>95900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>68100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>78800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>22200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>46600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>42100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>31400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>45900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>39800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>23300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>34300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>37300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>36500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>32400</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>28600</v>
       </c>
       <c r="AE18" s="3">
         <v>28600</v>
       </c>
       <c r="AF18" s="3">
+        <v>28600</v>
+      </c>
+      <c r="AG18" s="3">
         <v>22700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>18300</v>
       </c>
-      <c r="AH18" s="3" t="s">
+      <c r="AI18" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1781,8 +1814,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1820,11 +1854,11 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1847,11 +1881,11 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1876,403 +1910,418 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-      <c r="AH20" s="3" t="s">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>129700</v>
+      </c>
+      <c r="E21" s="3">
         <v>115700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>101100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>135700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>144700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>141900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>137100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>141800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>144400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>128600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>94800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>113800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>125400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>122400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>92400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>101700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>44400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>68800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>62800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>49800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>63600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>56900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>38300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>47600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>49300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>48000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>42800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>38200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>37800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>31600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>26600</v>
       </c>
-      <c r="AH21" s="3" t="s">
+      <c r="AI21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
         <v>2000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1100</v>
       </c>
       <c r="N22" s="3">
         <v>1100</v>
       </c>
       <c r="O22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3400</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>5400</v>
       </c>
       <c r="AG22" s="3">
         <v>5400</v>
       </c>
       <c r="AH22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AI22" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E23" s="3">
         <v>57400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>45300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>83500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>92100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>90700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>89400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>98600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>104700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>92800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>60000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>82300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>97300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>94600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>65800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>76800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>19800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>44900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>40400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>29400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>43700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>36800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>20500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>32100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>35100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>34700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>30000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>26000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>25300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>17300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>12900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E24" s="3">
         <v>7300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>17600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>20600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>19100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>20200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>22500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>22900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>21900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>18800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-12200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-11600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2369,204 +2418,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E26" s="3">
         <v>50000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>37100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>65900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>71500</v>
       </c>
       <c r="H26" s="3">
         <v>71500</v>
       </c>
       <c r="I26" s="3">
+        <v>71500</v>
+      </c>
+      <c r="J26" s="3">
         <v>69200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>76200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>81800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>71000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>49900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>74600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>82900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>75800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>57100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>68800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>32000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>37100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>35300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>41000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>43600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>30700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>17300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>26000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>39800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>31900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>30100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>23300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>20400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>11100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>16700</v>
       </c>
-      <c r="AH26" s="3" t="s">
+      <c r="AI26" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E27" s="3">
         <v>50000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>37100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>65900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>71500</v>
       </c>
       <c r="H27" s="3">
         <v>71500</v>
       </c>
       <c r="I27" s="3">
+        <v>71500</v>
+      </c>
+      <c r="J27" s="3">
         <v>69200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>76200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>81800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>71000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>49900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>74600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>82900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>75800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>57100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>68800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>32000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>37100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>35300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>41000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>43600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>30700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>17300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>26000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>39800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>31900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>30100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>23300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>20400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>11100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>16700</v>
       </c>
-      <c r="AH27" s="3" t="s">
+      <c r="AI27" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2663,8 +2721,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2713,17 +2774,17 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3" t="s">
+      <c r="U29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2731,23 +2792,23 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>600</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
         <v>600</v>
       </c>
       <c r="AA29" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>17800</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2761,8 +2822,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2859,8 +2923,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2957,8 +3024,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2996,11 +3066,11 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -3023,11 +3093,11 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -3052,109 +3122,115 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-      <c r="AH32" s="3" t="s">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E33" s="3">
         <v>50000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>37100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>65900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>71500</v>
       </c>
       <c r="H33" s="3">
         <v>71500</v>
       </c>
       <c r="I33" s="3">
+        <v>71500</v>
+      </c>
+      <c r="J33" s="3">
         <v>69200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>76200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>81800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>71000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>49900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>74600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>82900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>75800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>57100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>68800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>32000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>37100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>35300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>41000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>43600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>30700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>17900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>26600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>39800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>31900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>48000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>23300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>20400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>11100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>16700</v>
       </c>
-      <c r="AH33" s="3" t="s">
+      <c r="AI33" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3251,209 +3327,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E35" s="3">
         <v>50000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>37100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>65900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>71500</v>
       </c>
       <c r="H35" s="3">
         <v>71500</v>
       </c>
       <c r="I35" s="3">
+        <v>71500</v>
+      </c>
+      <c r="J35" s="3">
         <v>69200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>76200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>81800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>71000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>49900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>74600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>82900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>75800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>57100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>68800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>32000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>37100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>35300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>41000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>43600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>30700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>17900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>26600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>39800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>31900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>48000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>23300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>20400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>11100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>16700</v>
       </c>
-      <c r="AH35" s="3" t="s">
+      <c r="AI35" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45470</v>
+      </c>
+      <c r="E38" s="2">
         <v>45379</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45288</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45197</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45106</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45015</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44924</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44833</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44560</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44378</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44287</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44098</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44007</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43916</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43825</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43734</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43643</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43552</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43461</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43370</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43279</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43188</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43097</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43006</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42915</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42824</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42733</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3488,8 +3573,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3524,85 +3610,86 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>138100</v>
+      </c>
+      <c r="E41" s="3">
         <v>57400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>34400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>61600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>139400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>330100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>366100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>354100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>307800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>271100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>134400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>289900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>27000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>84100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>51500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>600</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>500</v>
       </c>
       <c r="AA41" s="3">
         <v>500</v>
       </c>
       <c r="AB41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AC41" s="3">
         <v>600</v>
@@ -3611,19 +3698,22 @@
         <v>600</v>
       </c>
       <c r="AE41" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AF41" s="3">
         <v>400</v>
       </c>
       <c r="AG41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH41" s="3">
         <v>500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3720,400 +3810,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>113400</v>
+      </c>
+      <c r="E43" s="3">
         <v>116800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>127400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>113900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>102300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>88000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>102100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>112400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>111700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>97800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>85000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>81500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>72800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>60000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>50400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>81000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>82100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>50600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>72200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>54500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>38500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>66100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>71900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>65900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>57200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>48000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>66500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>52600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>40600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>33400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>34500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>34800</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1037300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1032100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1106200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1105500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1172500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1181100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1292300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1320500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1344100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1149500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1008200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>833100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>683800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>607600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>654000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>598500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>594300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>588900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>581900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>484000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>446400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>437500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>471000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>403800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>432400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>426700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>428000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>395600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>367500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>316500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>293700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>301600</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E45" s="3">
         <v>49700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>48700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>55100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>56600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>54300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>53300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>56500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>49300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>43400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>40800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>49500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>42700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>40200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>28300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>23400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>19200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>21600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>20400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>21100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>27700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>23300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>15900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>16600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>12100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>11100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>8200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>9500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>7500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1342200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1256100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1316600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1336100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1335500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1328500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1457500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1497100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1511300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1322500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1273300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1294200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1165400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1061900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1040500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>974000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>830000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>951000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>701500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>643700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>564000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>527400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>559500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>486800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>502300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>486400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>503200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>456300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>416100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>359900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>336200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>343800</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4210,147 +4315,153 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3043100</v>
+      </c>
+      <c r="E48" s="3">
         <v>2969100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2912500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2869100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2701200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2576500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2463700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2321500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2263500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2144500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2032800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1918300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1782400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1558800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1495700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1396900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1354900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1338600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1278500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1169000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1102700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>998000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>328400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>300300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>271500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>245400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>221000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>200400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>183600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>163800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>150500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>135500</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>410000</v>
+      </c>
+      <c r="E49" s="3">
         <v>410900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>411800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>412700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>414600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>407100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>407800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>406300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>407100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>407300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>407400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>408200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>408900</v>
-      </c>
-      <c r="P49" s="3">
-        <v>336700</v>
       </c>
       <c r="Q49" s="3">
         <v>336700</v>
@@ -4368,7 +4479,7 @@
         <v>336700</v>
       </c>
       <c r="V49" s="3">
-        <v>336800</v>
+        <v>336700</v>
       </c>
       <c r="W49" s="3">
         <v>336800</v>
@@ -4406,8 +4517,11 @@
       <c r="AH49" s="3">
         <v>336800</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>336800</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4504,8 +4618,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4602,106 +4719,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E52" s="3">
         <v>22600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>20200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>23200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>8000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4798,106 +4921,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4818100</v>
+      </c>
+      <c r="E54" s="3">
         <v>4658700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4662600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4638100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4475500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4335200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4351200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4244700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4199400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3893400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3730700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3628100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3364300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2964700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2880400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2714400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2528700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2633900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2324300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2156900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2011100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1873400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1234100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1131900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1118400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1075900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1068000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1000900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>944200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>868400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>831200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>820400</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4932,8 +5061,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4968,106 +5098,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>698700</v>
+      </c>
+      <c r="E57" s="3">
         <v>641200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>679300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>706300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>664700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>572500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>590900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>642100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>770200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>688500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>661900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>634300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>529200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>402100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>417900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>362500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>326000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>319800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>368500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>318400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>272700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>229500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>313500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>237800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>265000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>255000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>258700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>249200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>243600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>205900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>158500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>165800</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5093,43 +5227,43 @@
         <v>2100</v>
       </c>
       <c r="K58" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="L58" s="3">
         <v>1600</v>
       </c>
       <c r="M58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N58" s="3">
         <v>2100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1800</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
       <c r="W58" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="X58" s="3">
         <v>3500</v>
@@ -5162,402 +5296,417 @@
         <v>3500</v>
       </c>
       <c r="AH58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AI58" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>448400</v>
+      </c>
+      <c r="E59" s="3">
         <v>430400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>470600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>466000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>449400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>432000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>413800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>417200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>425500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>403300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>368000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>376100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>325500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>268700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>279300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>253700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>205100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>184900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>184100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>174100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>148400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>165400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>87300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>82900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>66800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>72600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>97100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>91500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>75300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>83800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>81700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1149200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1073600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1152000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1174400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1116200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1006500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1006800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1061400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1197300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1093300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1032000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1012000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>860200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>673000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>698800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>618900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>533700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>506500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>552500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>492400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>424600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>398300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>404300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>324200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>335300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>331100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>359300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>344200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>322400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>293200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>243700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>194700</v>
+      </c>
+      <c r="E61" s="3">
         <v>194800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>194900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>195000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>230100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>301700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>405600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>371900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>264200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>195700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>195800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>195900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>195400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>195500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>207200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>206800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>207000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>413300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>142600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>143300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>140500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>143300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>141800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>142500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>156800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>169800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>185600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>183900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>178300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>351200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>387200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>157600</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1427500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1409400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1384600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1383200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1319400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1298500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1281800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1228800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1243700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1202000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1179700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1155300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1129000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1015500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>977000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>957200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>937600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>904800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>864800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>798100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>775100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>711800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>103700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>101500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>91600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>87400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>80300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>84600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>82300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>77800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>65900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5654,8 +5803,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5752,8 +5904,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5850,106 +6005,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2771500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2677900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2731600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2752600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2665700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2606800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2694100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2662000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2705100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2491000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2407500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2363200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2184700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1884000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1883000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1782900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1678200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1824600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1560000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1433800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1340200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1253400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>649800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>568200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>583700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>588300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>625100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>612800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>583100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>722200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>696900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>479100</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5984,8 +6145,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6082,8 +6244,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6180,8 +6345,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6278,8 +6446,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6376,106 +6547,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1523100</v>
+      </c>
+      <c r="E72" s="3">
         <v>1466400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1416400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1379300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1313400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1241900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1170400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1101200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1025000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>943200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>872200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>822400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>747700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>664800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>589000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>531900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>463100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>431100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>394000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>358700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>317700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>274100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>243600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>225700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>199100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>159200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>119600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>71600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>48300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>27900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>16800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6572,8 +6749,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6670,8 +6850,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6768,106 +6951,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2046600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1980800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1931000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1885500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1809800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1728400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1657200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1582600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1494300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1402400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1323200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1264900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1179600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1080700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>997400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>931500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>850500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>809300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>764300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>723000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>670900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>620000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>584300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>563700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>534700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>487600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>442900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>388200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>361100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>146100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>134300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>341400</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6964,209 +7153,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45470</v>
+      </c>
+      <c r="E80" s="2">
         <v>45379</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45288</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45197</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45106</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45015</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44924</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44833</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44560</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44378</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44287</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44098</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44007</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43916</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43825</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43734</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43643</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43552</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43461</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43370</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43279</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43188</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43097</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43006</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42915</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42824</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42733</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E81" s="3">
         <v>50000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>37100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>65900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>71500</v>
       </c>
       <c r="H81" s="3">
         <v>71500</v>
       </c>
       <c r="I81" s="3">
+        <v>71500</v>
+      </c>
+      <c r="J81" s="3">
         <v>69200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>76200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>81800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>71000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>49900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>74600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>82900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>75800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>57100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>68800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>32000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>37100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>35300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>41000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>43600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>30700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>17900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>26600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>39800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>31900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>48000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>23300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>20400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>11100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>16700</v>
       </c>
-      <c r="AH81" s="3" t="s">
+      <c r="AI81" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7201,106 +7399,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E83" s="3">
         <v>56400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>54900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>50900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>49700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>46400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>42300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>40100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>38000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>34600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>33700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>27700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>26400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>24400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>22900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>22300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>22100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>20700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>18400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>17700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>17200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>14900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>13400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>11500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>10400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>9600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>9100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>8900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>8300</v>
       </c>
-      <c r="AH83" s="3" t="s">
+      <c r="AI83" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7397,8 +7599,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7495,8 +7700,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7593,8 +7801,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7691,8 +7902,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7789,106 +8003,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>194000</v>
+      </c>
+      <c r="E89" s="3">
         <v>147500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>104600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>222300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>226400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>250300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>105100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-63600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>108300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>155600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>101000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>136500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>173000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>72000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>24700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>87400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>95100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>27000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>41900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>59800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>43300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>40600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>26300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>16400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>10400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>56100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>18500</v>
       </c>
-      <c r="AH89" s="3" t="s">
+      <c r="AI89" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7923,106 +8143,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-113900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-111700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-133900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-134500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-139800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-139400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-133800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-108500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-113400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-130000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-145600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-86200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-45900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-102800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-43700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-27600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-38400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-55000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-62800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-46500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-31600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-42000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-35600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-27800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-24100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-19800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AH91" s="3" t="s">
+      <c r="AI91" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8119,8 +8343,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8217,106 +8444,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-113900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-111700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-133900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-134700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-156900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-139400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-136500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-108500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-109200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-101400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-130000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-145800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-149600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-45900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-102800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-43700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-27600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-38400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-55000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-62800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-46500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-31600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-42000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-46000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-27800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-32600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-25700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-22400</v>
       </c>
-      <c r="AH94" s="3" t="s">
+      <c r="AI94" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8351,8 +8584,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8449,8 +8683,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8547,8 +8784,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8645,8 +8885,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8743,106 +8986,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-30100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-70300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-115600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>33400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>110600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>72400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>6000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>7400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-199900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>276600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>8100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-13800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>6300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>7900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>15300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-36300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>4000</v>
       </c>
-      <c r="AH100" s="3" t="s">
+      <c r="AI100" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8939,80 +9188,83 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>80600</v>
+      </c>
+      <c r="E102" s="3">
         <v>23000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-27200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>57500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-25700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-107600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-190600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-36000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>12000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>46300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>36600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>136700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-155500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>262900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-57100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>32700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>51000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>100</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
         <v>0</v>
       </c>
@@ -9023,18 +9275,21 @@
         <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>100</v>
       </c>
-      <c r="AH102" s="3" t="s">
+      <c r="AI102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
   <si>
     <t>FND</t>
   </si>
@@ -656,453 +656,466 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45561</v>
+      </c>
+      <c r="E7" s="2">
         <v>45470</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45379</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45288</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45197</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45106</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45015</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44924</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44833</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44560</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44378</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44287</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44098</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44007</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43916</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43825</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43734</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43643</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43552</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43461</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43370</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43279</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43188</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43097</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43006</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42915</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42824</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42733</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1117900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1133100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1097300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1048100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1107800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1135900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1122100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1048100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1097800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1089800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1028700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>914300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>876600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>860100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>782500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>723700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>684800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>462400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>554900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>527000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>521100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>520300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>477100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>436700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>435900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>434300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>402900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>389500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>343900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>344000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>307300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>278300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>271300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>642100</v>
+        <v>625400</v>
       </c>
       <c r="E9" s="3">
-        <v>627300</v>
+        <v>635300</v>
       </c>
       <c r="F9" s="3">
-        <v>606000</v>
+        <v>620200</v>
       </c>
       <c r="G9" s="3">
-        <v>640400</v>
+        <v>599800</v>
       </c>
       <c r="H9" s="3">
-        <v>656300</v>
+        <v>633500</v>
       </c>
       <c r="I9" s="3">
-        <v>652900</v>
+        <v>650700</v>
       </c>
       <c r="J9" s="3">
+        <v>646200</v>
+      </c>
+      <c r="K9" s="3">
         <v>612200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>650300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>653600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>620700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>559700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>511200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>494700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>445600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>416100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>390200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>265700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>318900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>297000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>307300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>302500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>275700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>255700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>257700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>256600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>237600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>227100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>201400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>201800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>181800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>163500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>160300</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>491000</v>
+        <v>492500</v>
       </c>
       <c r="E10" s="3">
-        <v>470000</v>
+        <v>497900</v>
       </c>
       <c r="F10" s="3">
-        <v>442100</v>
+        <v>477100</v>
       </c>
       <c r="G10" s="3">
-        <v>467400</v>
+        <v>448400</v>
       </c>
       <c r="H10" s="3">
-        <v>479600</v>
+        <v>474300</v>
       </c>
       <c r="I10" s="3">
-        <v>469200</v>
+        <v>485200</v>
       </c>
       <c r="J10" s="3">
+        <v>475800</v>
+      </c>
+      <c r="K10" s="3">
         <v>435900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>447500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>436200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>408000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>354600</v>
-      </c>
-      <c r="O10" s="3">
-        <v>365400</v>
       </c>
       <c r="P10" s="3">
         <v>365400</v>
       </c>
       <c r="Q10" s="3">
+        <v>365400</v>
+      </c>
+      <c r="R10" s="3">
         <v>336900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>307600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>294600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>196700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>236000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>230000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>213800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>217800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>201400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>181000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>178200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>177700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>165300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>162400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>142500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>142200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>125500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>114800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1138,8 +1151,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1239,8 +1253,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1340,34 +1357,37 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="E14" s="3">
+        <v>-700</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
-        <v>900</v>
+        <v>600</v>
+      </c>
+      <c r="G14" s="3">
+        <v>300</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
+        <v>1400</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1375,35 +1395,35 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1700</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-1000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1411,8 +1431,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1420,52 +1440,55 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>5400</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3">
         <v>1700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>57900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>58400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>56400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>54900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>50900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>49700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>46400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1542,8 +1565,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1576,210 +1602,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1061800</v>
+        <v>1051600</v>
       </c>
       <c r="E17" s="3">
-        <v>1038000</v>
+        <v>1062500</v>
       </c>
       <c r="F17" s="3">
-        <v>1002000</v>
+        <v>1037400</v>
       </c>
       <c r="G17" s="3">
+        <v>1001700</v>
+      </c>
+      <c r="H17" s="3">
         <v>1023000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1040900</v>
       </c>
-      <c r="I17" s="3">
-        <v>1026500</v>
-      </c>
       <c r="J17" s="3">
+        <v>1025100</v>
+      </c>
+      <c r="K17" s="3">
         <v>953300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>996200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>983400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>934800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>853200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>793200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>763300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>686600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>655600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>606000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>440200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>508300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>484900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>489700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>474400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>437300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>413400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>401600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>397000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>366400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>357100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>315300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>315400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>284600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>260000</v>
       </c>
-      <c r="AI17" s="3" t="s">
+      <c r="AJ17" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>71300</v>
+        <v>66300</v>
       </c>
       <c r="E18" s="3">
-        <v>59300</v>
+        <v>70700</v>
       </c>
       <c r="F18" s="3">
-        <v>46100</v>
+        <v>59900</v>
       </c>
       <c r="G18" s="3">
+        <v>46400</v>
+      </c>
+      <c r="H18" s="3">
         <v>84800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>95000</v>
       </c>
-      <c r="I18" s="3">
-        <v>95600</v>
-      </c>
       <c r="J18" s="3">
+        <v>97000</v>
+      </c>
+      <c r="K18" s="3">
         <v>94800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>101600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>106400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>93900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>61100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>83400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>96800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>95900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>68100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>78800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>22200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>46600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>42100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>31400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>45900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>39800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>23300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>34300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>37300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>36500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>32400</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>28600</v>
       </c>
       <c r="AF18" s="3">
         <v>28600</v>
       </c>
       <c r="AG18" s="3">
+        <v>28600</v>
+      </c>
+      <c r="AH18" s="3">
         <v>22700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>18300</v>
       </c>
-      <c r="AI18" s="3" t="s">
+      <c r="AJ18" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1815,31 +1848,32 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1857,11 +1891,11 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1884,11 +1918,11 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1913,415 +1947,430 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-      <c r="AI20" s="3" t="s">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>129700</v>
+        <v>124200</v>
       </c>
       <c r="E21" s="3">
-        <v>115700</v>
+        <v>129000</v>
       </c>
       <c r="F21" s="3">
-        <v>101100</v>
+        <v>116300</v>
       </c>
       <c r="G21" s="3">
+        <v>101400</v>
+      </c>
+      <c r="H21" s="3">
         <v>135700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>144700</v>
       </c>
-      <c r="I21" s="3">
-        <v>141900</v>
-      </c>
       <c r="J21" s="3">
+        <v>143300</v>
+      </c>
+      <c r="K21" s="3">
         <v>137100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>141800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>144400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>128600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>94800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>113800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>125400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>122400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>92400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>101700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>44400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>68800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>62800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>49800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>63600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>56900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>38300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>47600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>49300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>48000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>42800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>38200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>37800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>31600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>26600</v>
       </c>
-      <c r="AI21" s="3" t="s">
+      <c r="AJ21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="E22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F22" s="3">
         <v>2000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="L22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M22" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N22" s="3">
         <v>1200</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>5300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1100</v>
       </c>
       <c r="O22" s="3">
         <v>1100</v>
       </c>
       <c r="P22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3400</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>5400</v>
       </c>
       <c r="AH22" s="3">
         <v>5400</v>
       </c>
       <c r="AI22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E23" s="3">
         <v>70700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>57400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>45300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>83500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>92100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>90700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>89400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>98600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>104700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>92800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>60000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>82300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>97300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>94600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>65800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>76800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>19800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>44900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>40400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>29400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>43700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>36800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>20500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>32100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>35100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>34700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>30000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>26000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>25300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>17300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>12900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E24" s="3">
         <v>14000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>17600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>20600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>19100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>20200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>22500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>22900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>21900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>18800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-12200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-11600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>6100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-3800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2421,210 +2470,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E26" s="3">
         <v>56700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>50000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>37100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>65900</v>
-      </c>
-      <c r="H26" s="3">
-        <v>71500</v>
       </c>
       <c r="I26" s="3">
         <v>71500</v>
       </c>
       <c r="J26" s="3">
+        <v>71500</v>
+      </c>
+      <c r="K26" s="3">
         <v>69200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>76200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>81800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>71000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>49900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>74600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>82900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>75800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>57100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>68800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>32000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>37100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>35300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>41000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>43600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>30700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>17300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>26000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>39800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>31900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>30100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>23300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>20400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>11100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>16700</v>
       </c>
-      <c r="AI26" s="3" t="s">
+      <c r="AJ26" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E27" s="3">
         <v>56700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>50000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>37100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>65900</v>
-      </c>
-      <c r="H27" s="3">
-        <v>71500</v>
       </c>
       <c r="I27" s="3">
         <v>71500</v>
       </c>
       <c r="J27" s="3">
+        <v>71500</v>
+      </c>
+      <c r="K27" s="3">
         <v>69200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>76200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>81800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>71000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>49900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>74600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>82900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>75800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>57100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>68800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>32000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>37100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>35300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>41000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>43600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>30700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>17300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>26000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>39800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>31900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>30100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>23300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>20400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>11100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>16700</v>
       </c>
-      <c r="AI27" s="3" t="s">
+      <c r="AJ27" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2724,8 +2782,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2777,17 +2838,17 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2795,24 +2856,24 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>600</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
         <v>600</v>
       </c>
       <c r="AB29" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>17800</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2825,8 +2886,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2926,8 +2990,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3027,31 +3094,34 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3069,11 +3139,11 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3096,11 +3166,11 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -3125,112 +3195,118 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-      <c r="AI32" s="3" t="s">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E33" s="3">
         <v>56700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>50000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>37100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>65900</v>
-      </c>
-      <c r="H33" s="3">
-        <v>71500</v>
       </c>
       <c r="I33" s="3">
         <v>71500</v>
       </c>
       <c r="J33" s="3">
+        <v>71500</v>
+      </c>
+      <c r="K33" s="3">
         <v>69200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>76200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>81800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>71000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>49900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>74600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>82900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>75800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>57100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>68800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>32000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>37100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>35300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>41000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>43600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>30700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>17900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>26600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>39800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>31900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>48000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>23300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>20400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>11100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>16700</v>
       </c>
-      <c r="AI33" s="3" t="s">
+      <c r="AJ33" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3330,215 +3406,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E35" s="3">
         <v>56700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>50000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>37100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>65900</v>
-      </c>
-      <c r="H35" s="3">
-        <v>71500</v>
       </c>
       <c r="I35" s="3">
         <v>71500</v>
       </c>
       <c r="J35" s="3">
+        <v>71500</v>
+      </c>
+      <c r="K35" s="3">
         <v>69200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>76200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>81800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>71000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>49900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>74600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>82900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>75800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>57100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>68800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>32000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>37100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>35300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>41000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>43600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>30700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>17900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>26600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>39800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>31900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>48000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>23300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>20400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>11100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>16700</v>
       </c>
-      <c r="AI35" s="3" t="s">
+      <c r="AJ35" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45561</v>
+      </c>
+      <c r="E38" s="2">
         <v>45470</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45379</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45288</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45197</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45106</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45015</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44924</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44833</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44560</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44378</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44287</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44098</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44007</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43916</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43825</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43734</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43643</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43552</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43461</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43370</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43279</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43188</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43097</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43006</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42915</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42824</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42733</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3574,8 +3659,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3611,88 +3697,89 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>180800</v>
+      </c>
+      <c r="E41" s="3">
         <v>138100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>57400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>34400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>61600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>31800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>139400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>330100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>366100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>354100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>307800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>271100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>134400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>289900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>27000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>84100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>51500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>600</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>500</v>
       </c>
       <c r="AB41" s="3">
         <v>500</v>
       </c>
       <c r="AC41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AD41" s="3">
         <v>600</v>
@@ -3701,19 +3788,22 @@
         <v>600</v>
       </c>
       <c r="AF41" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AG41" s="3">
         <v>400</v>
       </c>
       <c r="AH41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI41" s="3">
         <v>500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3813,435 +3903,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>107700</v>
+      </c>
+      <c r="E43" s="3">
         <v>113400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>116800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>127400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>113900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>102300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>88000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>102100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>112400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>111700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>97800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>85000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>81500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>72800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>60000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>50400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>81000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>82100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>50600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>72200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>54500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>38500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>66100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>71900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>65900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>57200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>48000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>66500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>52600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>40600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>33400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>34500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>34800</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1046000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1037300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1032100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1106200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1105500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1172500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1181100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1292300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1320500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1344100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1149500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1008200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>833100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>683800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>607600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>654000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>598500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>594300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>588900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>581900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>484000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>446400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>437500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>471000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>403800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>432400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>426700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>428000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>395600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>367500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>316500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>293700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>301600</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>53400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>49700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>48700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>55100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>56600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>54300</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>53300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>56500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>49300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>43400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>40800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>49500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>42700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>40200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>28300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>23400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>19200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>21600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>20400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>21100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>27700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>23300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>15900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>16600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>12100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>11100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>8200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>7600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>9500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>7500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1388900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1342200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1256100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1316600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1336100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1335500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1328500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1457500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1497100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1511300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1322500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1273300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1294200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1165400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1061900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1040500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>974000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>830000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>951000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>701500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>643700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>564000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>527400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>559500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>486800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>502300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>486400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>503200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>456300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>416100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>359900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>336200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>343800</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4318,153 +4423,159 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3110600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3043100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2969100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2912500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2869100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2701200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2576500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2463700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2321500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2263500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2144500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2032800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1918300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1782400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1558800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1495700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1396900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1354900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1338600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1278500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1169000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1102700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>998000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>328400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>300300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>271500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>245400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>221000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>200400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>183600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>163800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>150500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>135500</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>409100</v>
+      </c>
+      <c r="E49" s="3">
         <v>410000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>410900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>411800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>412700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>414600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>407100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>407800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>406300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>407100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>407300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>407400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>408200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>408900</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>336700</v>
       </c>
       <c r="R49" s="3">
         <v>336700</v>
@@ -4482,7 +4593,7 @@
         <v>336700</v>
       </c>
       <c r="W49" s="3">
-        <v>336800</v>
+        <v>336700</v>
       </c>
       <c r="X49" s="3">
         <v>336800</v>
@@ -4520,8 +4631,11 @@
       <c r="AI49" s="3">
         <v>336800</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>336800</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4621,8 +4735,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4722,109 +4839,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>22700</v>
+        <v>7000</v>
       </c>
       <c r="E52" s="3">
-        <v>22600</v>
+        <v>7500</v>
       </c>
       <c r="F52" s="3">
-        <v>21600</v>
+        <v>7200</v>
       </c>
       <c r="G52" s="3">
-        <v>20200</v>
+        <v>5600</v>
       </c>
       <c r="H52" s="3">
-        <v>24200</v>
+        <v>7700</v>
       </c>
       <c r="I52" s="3">
-        <v>23200</v>
+        <v>8500</v>
       </c>
       <c r="J52" s="3">
+        <v>9100</v>
+      </c>
+      <c r="K52" s="3">
         <v>22200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>19200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>7600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4924,109 +5047,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4932200</v>
+      </c>
+      <c r="E54" s="3">
         <v>4818100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4658700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4662600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4638100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4475500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4335200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4351200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4244700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4199400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3893400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3730700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3628100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3364300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2964700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2880400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2714400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2528700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2633900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2324300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2156900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2011100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1873400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1234100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1131900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1118400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1075900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1068000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1000900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>944200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>868400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>831200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>820400</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5062,8 +5191,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5099,174 +5229,178 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>737800</v>
+      </c>
+      <c r="E57" s="3">
         <v>698700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>641200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>679300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>706300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>664700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>572500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>590900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>642100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>770200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>688500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>661900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>634300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>529200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>402100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>417900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>362500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>326000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>319800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>368500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>318400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>272700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>229500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>313500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>237800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>265000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>255000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>258700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>249200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>243600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>205900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>158500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>165800</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2100</v>
+        <v>136700</v>
       </c>
       <c r="E58" s="3">
-        <v>2100</v>
+        <v>134900</v>
       </c>
       <c r="F58" s="3">
-        <v>2100</v>
+        <v>131300</v>
       </c>
       <c r="G58" s="3">
-        <v>2100</v>
+        <v>128500</v>
       </c>
       <c r="H58" s="3">
-        <v>2100</v>
+        <v>127500</v>
       </c>
       <c r="I58" s="3">
-        <v>2100</v>
+        <v>121100</v>
       </c>
       <c r="J58" s="3">
-        <v>2100</v>
+        <v>115900</v>
       </c>
       <c r="K58" s="3">
         <v>2100</v>
       </c>
       <c r="L58" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="M58" s="3">
         <v>1600</v>
       </c>
       <c r="N58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O58" s="3">
         <v>2100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1800</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
       <c r="X58" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="Y58" s="3">
         <v>3500</v>
@@ -5299,414 +5433,429 @@
         <v>3500</v>
       </c>
       <c r="AI58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>448400</v>
+        <v>76400</v>
       </c>
       <c r="E59" s="3">
-        <v>430400</v>
+        <v>17500</v>
       </c>
       <c r="F59" s="3">
-        <v>470600</v>
+        <v>77400</v>
       </c>
       <c r="G59" s="3">
-        <v>466000</v>
+        <v>99500</v>
       </c>
       <c r="H59" s="3">
-        <v>449400</v>
+        <v>75800</v>
       </c>
       <c r="I59" s="3">
-        <v>432000</v>
+        <v>82500</v>
       </c>
       <c r="J59" s="3">
+        <v>87500</v>
+      </c>
+      <c r="K59" s="3">
         <v>413800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>417200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>425500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>403300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>368000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>376100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>325500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>268700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>279300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>253700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>205100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>184900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>184100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>174100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>148400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>165400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>87300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>82900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>66800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>72600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>97100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>91500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>75300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>83800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>81700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1193000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1149200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1073600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1152000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1174400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1116200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1006500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1006800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1061400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1197300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1093300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1032000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1012000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>860200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>673000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>698800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>618900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>533700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>506500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>552500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>492400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>424600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>398300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>404300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>324200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>335300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>331100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>359300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>344200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>322400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>293200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>243700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>194700</v>
+        <v>1563100</v>
       </c>
       <c r="E61" s="3">
-        <v>194800</v>
+        <v>1556900</v>
       </c>
       <c r="F61" s="3">
-        <v>194900</v>
+        <v>1532600</v>
       </c>
       <c r="G61" s="3">
-        <v>195000</v>
+        <v>1496700</v>
       </c>
       <c r="H61" s="3">
-        <v>230100</v>
+        <v>1520300</v>
       </c>
       <c r="I61" s="3">
-        <v>301700</v>
+        <v>1507100</v>
       </c>
       <c r="J61" s="3">
+        <v>1553300</v>
+      </c>
+      <c r="K61" s="3">
         <v>405600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>371900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>264200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>195700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>195800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>195900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>195400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>195500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>207200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>206800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>207000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>413300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>142600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>143300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>140500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>143300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>141800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>142500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>156800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>169800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>185600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>183900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>178300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>351200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>387200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>157600</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1427500</v>
+        <v>11600</v>
       </c>
       <c r="E62" s="3">
-        <v>1409400</v>
+        <v>11400</v>
       </c>
       <c r="F62" s="3">
-        <v>1384600</v>
+        <v>11200</v>
       </c>
       <c r="G62" s="3">
-        <v>1383200</v>
+        <v>15700</v>
       </c>
       <c r="H62" s="3">
-        <v>1319400</v>
+        <v>11000</v>
       </c>
       <c r="I62" s="3">
-        <v>1298500</v>
+        <v>10300</v>
       </c>
       <c r="J62" s="3">
+        <v>10100</v>
+      </c>
+      <c r="K62" s="3">
         <v>1281800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1228800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1243700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1202000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1179700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1155300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1129000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1015500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>977000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>957200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>937600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>904800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>864800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>798100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>775100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>711800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>103700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>101500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>91600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>87400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>80300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>84600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>82300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>77800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>65900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5806,8 +5955,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5907,8 +6059,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6008,109 +6163,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2821200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2771500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2677900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2731600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2752600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2665700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2606800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2694100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2662000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2705100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2491000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2407500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2363200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2184700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1884000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1883000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1782900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1678200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1824600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1560000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1433800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1340200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1253400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>649800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>568200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>583700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>588300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>625100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>612800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>583100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>722200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>696900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>479100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6146,8 +6307,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6247,8 +6409,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6348,8 +6513,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6449,8 +6617,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6550,109 +6721,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1574800</v>
+      </c>
+      <c r="E72" s="3">
         <v>1523100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1466400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1416400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1379300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1313400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1241900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1170400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1101200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1025000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>943200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>872200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>822400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>747700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>664800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>589000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>531900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>463100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>431100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>394000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>358700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>317700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>274100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>243600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>225700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>199100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>159200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>119600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>71600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>48300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>27900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>16800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6752,8 +6929,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6853,8 +7033,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6954,109 +7137,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2111100</v>
+      </c>
+      <c r="E76" s="3">
         <v>2046600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1980800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1931000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1885500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1809800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1728400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1657200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1582600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1494300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1402400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1323200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1264900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1179600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1080700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>997400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>931500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>850500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>809300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>764300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>723000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>670900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>620000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>584300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>563700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>534700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>487600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>442900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>388200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>361100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>146100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>134300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>341400</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7156,215 +7345,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45561</v>
+      </c>
+      <c r="E80" s="2">
         <v>45470</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45379</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45288</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45197</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45106</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45015</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44924</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44833</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44560</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44378</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44287</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44098</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44007</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43916</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43825</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43734</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43643</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43552</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43461</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43370</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43279</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43188</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43097</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43006</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42915</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42824</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42733</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E81" s="3">
         <v>56700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>50000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>37100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>65900</v>
-      </c>
-      <c r="H81" s="3">
-        <v>71500</v>
       </c>
       <c r="I81" s="3">
         <v>71500</v>
       </c>
       <c r="J81" s="3">
+        <v>71500</v>
+      </c>
+      <c r="K81" s="3">
         <v>69200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>76200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>81800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>71000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>49900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>74600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>82900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>75800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>57100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>68800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>32000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>37100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>35300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>41000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>43600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>30700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>17900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>26600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>39800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>31900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>48000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>23300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>20400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>11100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>16700</v>
       </c>
-      <c r="AI81" s="3" t="s">
+      <c r="AJ81" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7400,109 +7598,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>58400</v>
+        <v>50900</v>
       </c>
       <c r="E83" s="3">
-        <v>56400</v>
+        <v>49700</v>
       </c>
       <c r="F83" s="3">
-        <v>54900</v>
+        <v>46400</v>
       </c>
       <c r="G83" s="3">
-        <v>50900</v>
+        <v>39200</v>
       </c>
       <c r="H83" s="3">
-        <v>49700</v>
+        <v>40100</v>
       </c>
       <c r="I83" s="3">
-        <v>46400</v>
+        <v>38000</v>
       </c>
       <c r="J83" s="3">
+        <v>34600</v>
+      </c>
+      <c r="K83" s="3">
         <v>42300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>40100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>38000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>34600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>33700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>30400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>27700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>26400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>24400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>22900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>22300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>22100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>20700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>18400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>17700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>17200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>14900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>13400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>11500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>10400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>9600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>9100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>8900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>8300</v>
       </c>
-      <c r="AI83" s="3" t="s">
+      <c r="AJ83" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7602,8 +7804,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7703,8 +7908,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7804,8 +8012,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7905,8 +8116,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8006,109 +8220,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>160300</v>
+      </c>
+      <c r="E89" s="3">
         <v>194000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>147500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>104600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>222300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>226400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>250300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>105100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>11200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-63600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>108300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>155600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>101000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>136500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>173000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>72000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>24700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>87400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>95100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>27000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>41900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>59800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>43300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>40600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>26300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>16400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>10400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>56100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>18500</v>
       </c>
-      <c r="AI89" s="3" t="s">
+      <c r="AJ89" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8144,109 +8364,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-123700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-113900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-111700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-133900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-134500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-139800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-139400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-133800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-108500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-113400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-130000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-145600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-86200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-45900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-102800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-43700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-27600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-38400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-55000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-62800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-46500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-31600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-42000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-35600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-27800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-24100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-19800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AI91" s="3" t="s">
+      <c r="AJ91" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8346,8 +8570,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8447,109 +8674,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-123700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-113900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-111700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-133900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-134700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-156900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-139400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-136500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-108500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-109200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-101400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-130000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-145800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-149600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-45900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-102800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-43700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-27600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-38400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-55000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-62800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-46500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-31600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-46000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-27800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-32600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-25700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-22400</v>
       </c>
-      <c r="AI94" s="3" t="s">
+      <c r="AJ94" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8585,31 +8818,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8686,8 +8920,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8787,8 +9024,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8888,8 +9128,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8989,132 +9232,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E100" s="3">
         <v>600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-30100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-70300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-115600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>33400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>110600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>72400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-8800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>7400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-199900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>276600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>8100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>4400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-13800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>6300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>7900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>15300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-36300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>4000</v>
       </c>
-      <c r="AI100" s="3" t="s">
+      <c r="AJ100" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9191,83 +9440,86 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E102" s="3">
         <v>80600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>23000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-27200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>57500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-25700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-107600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-190600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-36000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>46300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>36600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>136700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-155500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>262900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-57100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>32700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>51000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
       <c r="AB102" s="3">
         <v>0</v>
       </c>
@@ -9278,18 +9530,21 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-100</v>
       </c>
-      <c r="AG102" s="3">
-        <v>0</v>
-      </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>100</v>
       </c>
-      <c r="AI102" s="3" t="s">
+      <c r="AJ102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>FND</t>
   </si>
@@ -656,466 +656,478 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45652</v>
+      </c>
+      <c r="E7" s="2">
         <v>45561</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45470</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45379</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45288</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45197</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45106</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45015</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44924</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44833</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44560</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44378</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44287</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44098</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44007</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43916</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43825</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43734</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43643</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43552</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43461</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43370</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43279</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43188</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43097</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43006</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42915</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42824</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42733</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1107400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1117900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1133100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1097300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1048100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1107800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1135900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1122100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1048100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1097800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1089800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1028700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>914300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>876600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>860100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>782500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>723700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>684800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>462400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>554900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>527000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>521100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>520300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>477100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>436700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>435900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>434300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>402900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>389500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>343900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>344000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>307300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>278300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>271300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>619200</v>
+      </c>
+      <c r="E9" s="3">
         <v>625400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>635300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>620200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>599800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>633500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>650700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>646200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>612200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>650300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>653600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>620700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>559700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>511200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>494700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>445600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>416100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>390200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>265700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>318900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>297000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>307300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>302500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>275700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>255700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>257700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>256600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>237600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>227100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>201400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>201800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>181800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>163500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>160300</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>488200</v>
+      </c>
+      <c r="E10" s="3">
         <v>492500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>497900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>477100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>448400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>474300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>485200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>475800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>435900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>447500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>436200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>408000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>354600</v>
-      </c>
-      <c r="P10" s="3">
-        <v>365400</v>
       </c>
       <c r="Q10" s="3">
         <v>365400</v>
       </c>
       <c r="R10" s="3">
+        <v>365400</v>
+      </c>
+      <c r="S10" s="3">
         <v>336900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>307600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>294600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>196700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>236000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>230000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>213800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>217800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>201400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>181000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>178200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>177700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>165300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>162400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>142500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>142200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>125500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>114800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1152,8 +1164,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1256,8 +1269,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1360,37 +1376,40 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>-700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3">
-        <v>300</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>900</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>1400</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1398,35 +1417,35 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>1700</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-1000</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1434,8 +1453,8 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1443,56 +1462,59 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>5400</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E15" s="3">
         <v>57900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>58400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>56400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>54900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>50900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>49700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>46400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1568,8 +1590,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1603,216 +1628,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1055000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1051600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1062500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1037400</v>
       </c>
-      <c r="G17" s="3">
-        <v>1001700</v>
-      </c>
       <c r="H17" s="3">
+        <v>1001100</v>
+      </c>
+      <c r="I17" s="3">
         <v>1023000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1040900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1025100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>953300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>996200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>983400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>934800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>853200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>793200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>763300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>686600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>655600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>606000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>440200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>508300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>484900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>489700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>474400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>437300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>413400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>401600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>397000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>366400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>357100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>315300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>315400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>284600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>260000</v>
       </c>
-      <c r="AJ17" s="3" t="s">
+      <c r="AK17" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E18" s="3">
         <v>66300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>70700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>59900</v>
       </c>
-      <c r="G18" s="3">
-        <v>46400</v>
-      </c>
       <c r="H18" s="3">
+        <v>47100</v>
+      </c>
+      <c r="I18" s="3">
         <v>84800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>95000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>97000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>94800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>101600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>106400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>93900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>61100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>83400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>96800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>95900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>68100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>78800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>22200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>46600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>42100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>31400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>45900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>39800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>23300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>34300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>37300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>36500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>32400</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>28600</v>
       </c>
       <c r="AG18" s="3">
         <v>28600</v>
       </c>
       <c r="AH18" s="3">
+        <v>28600</v>
+      </c>
+      <c r="AI18" s="3">
         <v>22700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>18300</v>
       </c>
-      <c r="AJ18" s="3" t="s">
+      <c r="AK18" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1849,8 +1881,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1875,8 +1908,8 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1894,11 +1927,11 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1921,11 +1954,11 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -1950,427 +1983,442 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
-      <c r="AJ20" s="3" t="s">
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E21" s="3">
         <v>124200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>129000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>116300</v>
       </c>
-      <c r="G21" s="3">
-        <v>101400</v>
-      </c>
       <c r="H21" s="3">
+        <v>102000</v>
+      </c>
+      <c r="I21" s="3">
         <v>135700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>144700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>143300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>137100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>141800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>144400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>128600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>94800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>113800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>125400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>122400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>92400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>101700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>44400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>68800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>62800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>49800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>63600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>56900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>38300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>47600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>49300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>48000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>42800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>38200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>37800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>31600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>26600</v>
       </c>
-      <c r="AJ21" s="3" t="s">
+      <c r="AK21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2000</v>
       </c>
-      <c r="G22" s="3">
-        <v>900</v>
-      </c>
       <c r="H22" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I22" s="3">
         <v>2600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1200</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1100</v>
       </c>
       <c r="P22" s="3">
         <v>1100</v>
       </c>
       <c r="Q22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R22" s="3">
         <v>400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>3400</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>5400</v>
       </c>
       <c r="AI22" s="3">
         <v>5400</v>
       </c>
       <c r="AJ22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AK22" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E23" s="3">
         <v>66100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>70700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>57400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>45300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>83500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>92100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>90700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>89400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>98600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>104700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>92800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>60000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>82300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>97300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>94600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>65800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>76800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>19800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>44900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>40400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>29400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>43700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>36800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>20500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>32100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>35100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>34700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>30000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>26000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>25300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>17300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>12900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E24" s="3">
         <v>14400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>17600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>20600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>19100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>20200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>22500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>22900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>21900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>18800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-12200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-11600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>6100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-3800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2473,216 +2521,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E26" s="3">
         <v>51700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>56700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>50000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>37100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>65900</v>
-      </c>
-      <c r="I26" s="3">
-        <v>71500</v>
       </c>
       <c r="J26" s="3">
         <v>71500</v>
       </c>
       <c r="K26" s="3">
+        <v>71500</v>
+      </c>
+      <c r="L26" s="3">
         <v>69200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>76200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>81800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>71000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>49900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>74600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>82900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>75800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>57100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>68800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>32000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>37100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>35300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>41000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>43600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>30700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>17300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>26000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>39800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>31900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>30100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>23300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>20400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>11100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>16700</v>
       </c>
-      <c r="AJ26" s="3" t="s">
+      <c r="AK26" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E27" s="3">
         <v>51700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>56700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>50000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>37100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>65900</v>
-      </c>
-      <c r="I27" s="3">
-        <v>71500</v>
       </c>
       <c r="J27" s="3">
         <v>71500</v>
       </c>
       <c r="K27" s="3">
+        <v>71500</v>
+      </c>
+      <c r="L27" s="3">
         <v>69200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>76200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>81800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>71000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>49900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>74600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>82900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>75800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>57100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>68800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>32000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>37100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>35300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>41000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>43600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>30700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>17300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>26000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>39800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>31900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>30100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>23300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>20400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>11100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>16700</v>
       </c>
-      <c r="AJ27" s="3" t="s">
+      <c r="AK27" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2785,8 +2842,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2841,17 +2901,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2859,24 +2919,24 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>600</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
         <v>600</v>
       </c>
       <c r="AC29" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>17800</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2889,8 +2949,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2993,8 +3056,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3097,8 +3163,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3123,8 +3192,8 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -3142,11 +3211,11 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -3169,11 +3238,11 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -3198,115 +3267,121 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
-      <c r="AJ32" s="3" t="s">
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E33" s="3">
         <v>51700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>56700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>50000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>37100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>65900</v>
-      </c>
-      <c r="I33" s="3">
-        <v>71500</v>
       </c>
       <c r="J33" s="3">
         <v>71500</v>
       </c>
       <c r="K33" s="3">
+        <v>71500</v>
+      </c>
+      <c r="L33" s="3">
         <v>69200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>76200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>81800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>71000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>49900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>74600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>82900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>75800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>57100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>68800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>32000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>37100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>35300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>41000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>43600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>30700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>17900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>26600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>39800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>31900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>48000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>23300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>20400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>11100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>16700</v>
       </c>
-      <c r="AJ33" s="3" t="s">
+      <c r="AK33" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3409,221 +3484,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E35" s="3">
         <v>51700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>56700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>50000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>37100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>65900</v>
-      </c>
-      <c r="I35" s="3">
-        <v>71500</v>
       </c>
       <c r="J35" s="3">
         <v>71500</v>
       </c>
       <c r="K35" s="3">
+        <v>71500</v>
+      </c>
+      <c r="L35" s="3">
         <v>69200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>76200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>81800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>71000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>49900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>74600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>82900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>75800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>57100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>68800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>32000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>37100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>35300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>41000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>43600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>30700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>17900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>26600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>39800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>31900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>48000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>23300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>20400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>11100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>16700</v>
       </c>
-      <c r="AJ35" s="3" t="s">
+      <c r="AK35" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45652</v>
+      </c>
+      <c r="E38" s="2">
         <v>45561</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45470</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45379</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45288</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45197</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45106</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45015</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44924</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44833</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44560</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44378</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44287</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44098</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44007</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43916</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43825</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43734</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43643</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43552</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43461</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43370</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43279</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43188</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43097</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43006</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42915</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42824</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42733</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3660,8 +3744,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3698,91 +3783,92 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>187700</v>
+      </c>
+      <c r="E41" s="3">
         <v>180800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>138100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>57400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>34400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>61600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>31800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>139400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>330100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>366100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>354100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>307800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>271100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>134400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>289900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>27000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>84100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>51500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>600</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>500</v>
       </c>
       <c r="AC41" s="3">
         <v>500</v>
       </c>
       <c r="AD41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AE41" s="3">
         <v>600</v>
@@ -3791,19 +3877,22 @@
         <v>600</v>
       </c>
       <c r="AG41" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AH41" s="3">
         <v>400</v>
       </c>
       <c r="AI41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3820,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -3906,221 +3995,230 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>115400</v>
+      </c>
+      <c r="E43" s="3">
         <v>107700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>113400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>116800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>127400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>113900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>102300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>88000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>102100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>112400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>111700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>97800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>85000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>81500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>72800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>60000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>50400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>81000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>82100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>50600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>72200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>54500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>38500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>66100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>71900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>65900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>57200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>48000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>66500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>52600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>40600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>33400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>34500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>34800</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1132600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1046000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1037300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1032100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1106200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1105500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1172500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1181100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1292300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1320500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1344100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1149500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1008200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>833100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>683800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>607600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>654000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>598500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>594300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>588900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>581900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>484000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>446400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>437500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>471000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>403800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>432400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>426700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>428000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>395600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>367500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>316500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>293700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>301600</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>7800</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
@@ -4140,195 +4238,201 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>53300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>56500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>49300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>43400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>40800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>49500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>42700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>40200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>28300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>23400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>19200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>21600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>20400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>21100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>27700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>23300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>15900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>16600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>12100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>11100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>8200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>7500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>7600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>9500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1492400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1388900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1342200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1256100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1316600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1336100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1335500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1328500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1457500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1497100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1511300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1322500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1273300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1294200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1165400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1061900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1040500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>974000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>830000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>951000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>701500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>643700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>564000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>527400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>559500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>486800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>502300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>486400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>503200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>456300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>416100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>359900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>336200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>343800</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>0</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
@@ -4348,8 +4452,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4426,159 +4530,165 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3117800</v>
+      </c>
+      <c r="E48" s="3">
         <v>3110600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3043100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2969100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2912500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2869100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2701200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2576500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2463700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2321500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2263500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2144500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2032800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1918300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1782400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1558800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1495700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1396900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1354900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1338600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1278500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1169000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1102700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>998000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>328400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>300300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>271500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>245400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>221000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>200400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>183600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>163800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>150500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>135500</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>408100</v>
+      </c>
+      <c r="E49" s="3">
         <v>409100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>410000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>410900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>411800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>412700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>414600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>407100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>407800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>406300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>407100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>407300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>407400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>408200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>408900</v>
-      </c>
-      <c r="R49" s="3">
-        <v>336700</v>
       </c>
       <c r="S49" s="3">
         <v>336700</v>
@@ -4596,7 +4706,7 @@
         <v>336700</v>
       </c>
       <c r="X49" s="3">
-        <v>336800</v>
+        <v>336700</v>
       </c>
       <c r="Y49" s="3">
         <v>336800</v>
@@ -4634,8 +4744,11 @@
       <c r="AJ49" s="3">
         <v>336800</v>
       </c>
+      <c r="AK49" s="3">
+        <v>336800</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4738,8 +4851,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4842,112 +4958,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E52" s="3">
         <v>7000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>19200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>7800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>7600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5050,112 +5172,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5050500</v>
+      </c>
+      <c r="E54" s="3">
         <v>4932200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4818100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4658700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4662600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4638100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4475500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4335200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4351200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4244700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4199400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3893400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3730700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3628100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3364300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2964700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2880400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2714400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2528700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2633900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2324300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2156900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2011100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1873400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1234100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1131900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1118400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1075900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1068000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1000900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>944200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>868400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>831200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>820400</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5192,8 +5320,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5230,180 +5359,184 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>794900</v>
+      </c>
+      <c r="E57" s="3">
         <v>737800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>698700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>641200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>679300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>706300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>664700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>572500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>590900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>642100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>770200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>688500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>661900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>634300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>529200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>402100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>417900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>362500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>326000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>319800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>368500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>318400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>272700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>229500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>313500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>237800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>265000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>255000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>258700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>249200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>243600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>205900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>158500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>165800</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>140700</v>
+      </c>
+      <c r="E58" s="3">
         <v>136700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>134900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>131300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>128500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>127500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>121100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>115900</v>
-      </c>
-      <c r="K58" s="3">
-        <v>2100</v>
       </c>
       <c r="L58" s="3">
         <v>2100</v>
       </c>
       <c r="M58" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="N58" s="3">
         <v>1600</v>
       </c>
       <c r="O58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P58" s="3">
         <v>2100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1800</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
         <v>0</v>
       </c>
       <c r="Y58" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="3">
         <v>3500</v>
@@ -5436,426 +5569,441 @@
         <v>3500</v>
       </c>
       <c r="AJ58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AK58" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>96700</v>
+      </c>
+      <c r="E59" s="3">
         <v>76400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>77400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>99500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>75800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>82500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>87500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>413800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>417200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>425500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>403300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>368000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>376100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>325500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>268700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>279300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>253700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>205100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>184900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>184100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>174100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>148400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>165400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>87300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>82900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>66800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>72600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>97100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>91500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>75300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>83800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>81700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1244200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1193000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1149200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1073600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1152000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1174400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1116200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1006500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1006800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1061400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1197300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1093300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1032000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1012000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>860200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>673000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>698800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>618900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>533700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>506500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>552500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>492400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>424600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>398300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>404300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>324200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>335300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>331100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>359300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>344200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>322400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>293200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>243700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1545800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1563100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1556900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1532600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1496700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1520300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1507100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1553300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>405600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>371900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>264200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>195700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>195800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>195900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>195400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>195500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>207200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>206800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>207000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>413300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>142600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>143300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>140500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>143300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>141800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>142500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>156800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>169800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>185600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>183900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>178300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>351200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>387200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>157600</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E62" s="3">
         <v>11600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1281800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1228800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1243700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1202000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1179700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1155300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1129000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1015500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>977000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>957200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>937600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>904800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>864800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>798100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>775100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>711800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>103700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>101500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>91600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>87400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>80300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>84600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>82300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>77800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>65900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5958,8 +6106,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6062,8 +6213,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6166,112 +6320,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2880300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2821200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2771500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2677900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2731600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2752600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2665700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2606800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2694100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2662000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2705100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2491000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2407500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2363200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2184700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1884000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1883000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1782900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1678200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1824600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1560000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1433800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1340200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1253400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>649800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>568200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>583700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>588300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>625100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>612800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>583100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>722200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>696900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>479100</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6308,8 +6468,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6412,8 +6573,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6516,8 +6680,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6620,8 +6787,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6724,112 +6894,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1622300</v>
+      </c>
+      <c r="E72" s="3">
         <v>1574800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1523100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1466400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1416400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1379300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1313400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1241900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1170400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1101200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1025000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>943200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>872200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>822400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>747700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>664800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>589000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>531900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>463100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>431100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>394000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>358700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>317700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>274100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>243600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>225700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>199100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>159200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>119600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>71600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>48300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>27900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>16800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6932,8 +7108,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7036,8 +7215,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7140,112 +7322,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2170200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2111100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2046600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1980800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1931000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1885500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1809800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1728400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1657200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1582600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1494300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1402400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1323200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1264900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1179600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1080700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>997400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>931500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>850500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>809300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>764300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>723000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>670900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>620000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>584300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>563700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>534700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>487600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>442900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>388200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>361100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>146100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>134300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>341400</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7348,221 +7536,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45652</v>
+      </c>
+      <c r="E80" s="2">
         <v>45561</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45470</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45379</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45288</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45197</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45106</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45015</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44924</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44833</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44560</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44378</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44287</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44098</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44007</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43916</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43825</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43734</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43643</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43552</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43461</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43370</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43279</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43188</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43097</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43006</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42915</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42824</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42733</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E81" s="3">
         <v>51700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>56700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>50000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>37100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>65900</v>
-      </c>
-      <c r="I81" s="3">
-        <v>71500</v>
       </c>
       <c r="J81" s="3">
         <v>71500</v>
       </c>
       <c r="K81" s="3">
+        <v>71500</v>
+      </c>
+      <c r="L81" s="3">
         <v>69200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>76200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>81800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>71000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>49900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>74600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>82900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>75800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>57100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>68800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>32000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>37100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>35300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>41000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>43600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>30700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>17900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>26600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>39800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>31900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>48000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>23300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>20400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>11100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>16700</v>
       </c>
-      <c r="AJ81" s="3" t="s">
+      <c r="AK81" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7599,112 +7796,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E83" s="3">
         <v>50900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>49700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>46400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>39200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>40100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>38000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>42300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>40100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>38000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>34600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>33700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>30400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>27700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>26400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>24400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>22900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>22300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>22100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>20700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>18400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>17700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>17200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>14900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>13400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>11500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>10400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>9600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>9100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>8900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>8300</v>
       </c>
-      <c r="AJ83" s="3" t="s">
+      <c r="AK83" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7807,8 +8008,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7911,8 +8115,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8015,8 +8222,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8119,8 +8329,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8223,112 +8436,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>101400</v>
+      </c>
+      <c r="E89" s="3">
         <v>160300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>194000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>147500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>104600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>222300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>226400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>250300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>105100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>11200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-63600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>108300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>155600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>101000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>136500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>173000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>72000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>24700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>87400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>95100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>27000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>41900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>59800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>43300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>40600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>26300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>16400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>10400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>56100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>18500</v>
       </c>
-      <c r="AJ89" s="3" t="s">
+      <c r="AK89" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8365,112 +8584,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-97500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-123700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-113900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-111700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-133900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-134500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-139800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-139400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-133800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-108500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-113400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-130000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-145600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-86200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-45900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-102800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-43700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-27600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-38400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-55000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-62800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-46500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-42000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-35600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-27800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-24100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-19800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AJ91" s="3" t="s">
+      <c r="AK91" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8573,8 +8796,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8677,112 +8903,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-97500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-123700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-113900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-111700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-133900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-134700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-156900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-139400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-136500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-108500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-109200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-101400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-130000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-145800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-149600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-45900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-102800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-43700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-27600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-38400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-55000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-62800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-46500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-31600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-46000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-27800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-32600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-25700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-22400</v>
       </c>
-      <c r="AJ94" s="3" t="s">
+      <c r="AK94" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8819,8 +9051,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8845,8 +9078,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8923,8 +9156,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9027,8 +9263,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9131,8 +9370,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9235,112 +9477,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>6200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-30100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-70300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-115600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>33400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>110600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>72400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>6000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>7400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-199900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>276600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>8100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-13800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>6300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>7900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>15300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-36300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ100" s="3" t="s">
+      <c r="AK100" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9365,8 +9613,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9443,86 +9691,89 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E102" s="3">
         <v>42700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>80600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>23000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>57500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-25700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-107600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-190600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>12000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>46300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>36600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>136700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-155500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>262900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-57100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>32700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>51000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>100</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
       <c r="AC102" s="3">
         <v>0</v>
       </c>
@@ -9533,18 +9784,21 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
-      <c r="AH102" s="3">
-        <v>0</v>
-      </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>100</v>
       </c>
-      <c r="AJ102" s="3" t="s">
+      <c r="AK102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>FND</t>
   </si>
@@ -656,478 +656,491 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45743</v>
+      </c>
+      <c r="E7" s="2">
         <v>45652</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45470</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45379</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45288</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45197</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45106</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45015</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44924</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44833</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44560</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44378</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44287</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44098</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44007</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43916</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43825</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43734</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43643</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43552</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43461</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43370</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43279</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43188</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43097</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43006</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42915</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42824</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42733</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1160700</v>
+      </c>
+      <c r="E8" s="3">
         <v>1107400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1117900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1133100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1097300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1048100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1107800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1135900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1122100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1048100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1097800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1089800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1028700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>914300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>876600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>860100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>782500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>723700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>684800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>462400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>554900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>527000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>521100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>520300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>477100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>436700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>435900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>434300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>402900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>389500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>343900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>344000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>307300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>278300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>271300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>641400</v>
+      </c>
+      <c r="E9" s="3">
         <v>619200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>625400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>635300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>620200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>599800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>633500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>650700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>646200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>612200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>650300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>653600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>620700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>559700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>511200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>494700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>445600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>416100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>390200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>265700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>318900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>297000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>307300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>302500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>275700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>255700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>257700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>256600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>237600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>227100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>201400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>201800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>181800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>163500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>160300</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>519300</v>
+      </c>
+      <c r="E10" s="3">
         <v>488200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>492500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>497900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>477100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>448400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>474300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>485200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>475800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>435900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>447500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>436200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>408000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>354600</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>365400</v>
       </c>
       <c r="R10" s="3">
         <v>365400</v>
       </c>
       <c r="S10" s="3">
+        <v>365400</v>
+      </c>
+      <c r="T10" s="3">
         <v>336900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>307600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>294600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>196700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>236000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>230000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>213800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>217800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>201400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>181000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>178200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>177700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>165300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>162400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>142500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>142200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>125500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>114800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1165,8 +1178,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1272,8 +1286,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1379,40 +1396,43 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-6800</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>-700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>1400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1420,35 +1440,35 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>1700</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-1000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
@@ -1456,8 +1476,8 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1465,59 +1485,62 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>5400</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3">
         <v>1700</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E15" s="3">
         <v>59800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>57900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>58400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>56400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>54900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>50900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>49700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>46400</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1593,8 +1616,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1629,222 +1655,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1096900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1055000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1051600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1062500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1037400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1001100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1023000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1040900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1025100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>953300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>996200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>983400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>934800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>853200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>793200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>763300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>686600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>655600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>606000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>440200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>508300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>484900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>489700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>474400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>437300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>413400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>401600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>397000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>366400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>357100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>315300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>315400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>284600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>260000</v>
       </c>
-      <c r="AK17" s="3" t="s">
+      <c r="AL17" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>63900</v>
+      </c>
+      <c r="E18" s="3">
         <v>52400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>66300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>70700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>59900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>47100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>84800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>95000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>97000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>94800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>101600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>106400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>93900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>61100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>83400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>96800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>95900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>68100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>78800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>22200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>46600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>42100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>31400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>45900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>39800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>23300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>34300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>37300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>36500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>32400</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>28600</v>
       </c>
       <c r="AH18" s="3">
         <v>28600</v>
       </c>
       <c r="AI18" s="3">
+        <v>28600</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>22700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>18300</v>
       </c>
-      <c r="AK18" s="3" t="s">
+      <c r="AL18" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1882,8 +1915,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1911,8 +1945,8 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1930,11 +1964,11 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1957,11 +1991,11 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1986,439 +2020,454 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
-      <c r="AK20" s="3" t="s">
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>123800</v>
+      </c>
+      <c r="E21" s="3">
         <v>112200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>124200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>129000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>116300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>102000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>135700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>144700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>143300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>137100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>141800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>144400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>128600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>94800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>113800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>125400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>122400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>92400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>101700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>44400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>68800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>62800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>49800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>63600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>56900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>38300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>47600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>49300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>48000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>42800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>38200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>37800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>31600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>26600</v>
       </c>
-      <c r="AK21" s="3" t="s">
+      <c r="AL21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E22" s="3">
         <v>-1900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1200</v>
       </c>
-      <c r="G22" s="3">
-        <v>2000</v>
-      </c>
       <c r="H22" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I22" s="3">
         <v>-2800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1200</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1100</v>
       </c>
       <c r="Q22" s="3">
         <v>1100</v>
       </c>
       <c r="R22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>2600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>3400</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>5400</v>
       </c>
       <c r="AJ22" s="3">
         <v>5400</v>
       </c>
       <c r="AK22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AL22" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>62700</v>
+      </c>
+      <c r="E23" s="3">
         <v>59300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>66100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>70700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>57400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>45300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>83500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>92100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>90700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>89400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>98600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>104700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>92800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>60000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>82300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>97300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>94600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>65800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>76800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>19800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>44900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>40400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>29400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>43700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>36800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>20500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>32100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>35100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>34700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>30000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>26000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>25300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>17300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>12900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E24" s="3">
         <v>11800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>17600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>20600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>19100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>20200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>22500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>22900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>21900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>18800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-12200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-11600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>6100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-3800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2524,222 +2573,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E26" s="3">
         <v>47500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>51700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>56700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>50000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>37100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>65900</v>
-      </c>
-      <c r="J26" s="3">
-        <v>71500</v>
       </c>
       <c r="K26" s="3">
         <v>71500</v>
       </c>
       <c r="L26" s="3">
+        <v>71500</v>
+      </c>
+      <c r="M26" s="3">
         <v>69200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>76200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>81800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>71000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>49900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>74600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>82900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>75800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>57100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>68800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>32000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>37100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>35300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>41000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>43600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>30700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>17300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>26000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>39800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>31900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>30100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>23300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>20400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>16700</v>
       </c>
-      <c r="AK26" s="3" t="s">
+      <c r="AL26" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E27" s="3">
         <v>47500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>51700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>56700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>50000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>37100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>65900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>71500</v>
       </c>
       <c r="K27" s="3">
         <v>71500</v>
       </c>
       <c r="L27" s="3">
+        <v>71500</v>
+      </c>
+      <c r="M27" s="3">
         <v>69200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>76200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>81800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>71000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>49900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>74600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>82900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>75800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>57100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>68800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>32000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>37100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>35300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>41000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>43600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>30700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>17300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>26000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>39800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>31900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>30100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>23300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>20400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>16700</v>
       </c>
-      <c r="AK27" s="3" t="s">
+      <c r="AL27" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2845,8 +2903,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2904,17 +2965,17 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2922,24 +2983,24 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>600</v>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC29" s="3">
         <v>600</v>
       </c>
       <c r="AD29" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>17800</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2952,8 +3013,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3059,8 +3123,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3166,8 +3233,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3195,8 +3265,8 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3214,11 +3284,11 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -3241,11 +3311,11 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -3270,118 +3340,124 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
-      <c r="AK32" s="3" t="s">
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E33" s="3">
         <v>47500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>51700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>56700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>50000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>37100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>65900</v>
-      </c>
-      <c r="J33" s="3">
-        <v>71500</v>
       </c>
       <c r="K33" s="3">
         <v>71500</v>
       </c>
       <c r="L33" s="3">
+        <v>71500</v>
+      </c>
+      <c r="M33" s="3">
         <v>69200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>76200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>81800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>71000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>49900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>74600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>82900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>75800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>57100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>68800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>32000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>37100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>35300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>41000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>43600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>30700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>17900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>26600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>39800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>31900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>48000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>23300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>20400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>16700</v>
       </c>
-      <c r="AK33" s="3" t="s">
+      <c r="AL33" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3487,227 +3563,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E35" s="3">
         <v>47500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>51700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>56700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>50000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>37100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>65900</v>
-      </c>
-      <c r="J35" s="3">
-        <v>71500</v>
       </c>
       <c r="K35" s="3">
         <v>71500</v>
       </c>
       <c r="L35" s="3">
+        <v>71500</v>
+      </c>
+      <c r="M35" s="3">
         <v>69200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>76200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>81800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>71000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>49900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>74600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>82900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>75800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>57100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>68800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>32000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>37100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>35300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>41000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>43600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>30700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>17900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>26600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>39800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>31900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>48000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>23300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>20400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>16700</v>
       </c>
-      <c r="AK35" s="3" t="s">
+      <c r="AL35" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45743</v>
+      </c>
+      <c r="E38" s="2">
         <v>45652</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45470</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45379</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45288</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45197</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45106</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45015</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44924</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44833</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44560</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44378</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44287</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44098</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44007</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43916</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43825</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43734</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43643</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43552</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43461</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43370</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43279</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43188</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43097</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43006</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42915</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42824</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42733</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3745,8 +3830,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3784,94 +3870,95 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>186900</v>
+      </c>
+      <c r="E41" s="3">
         <v>187700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>180800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>138100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>57400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>34400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>61600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>31800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>139400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>330100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>366100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>354100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>307800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>271100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>134400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>289900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>27000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>84100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>51500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>600</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>500</v>
       </c>
       <c r="AD41" s="3">
         <v>500</v>
       </c>
       <c r="AE41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AF41" s="3">
         <v>600</v>
@@ -3880,19 +3967,22 @@
         <v>600</v>
       </c>
       <c r="AH41" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AI41" s="3">
         <v>400</v>
       </c>
       <c r="AJ41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AK41" s="3">
         <v>500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3909,11 +3999,11 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>1800</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -3998,231 +4088,240 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>105500</v>
+      </c>
+      <c r="E43" s="3">
         <v>115400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>107700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>113400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>116800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>127400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>113900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>102300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>88000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>102100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>112400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>111700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>97800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>85000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>81500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>72800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>60000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>50400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>81000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>82100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>50600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>72200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>54500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>38500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>66100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>71900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>65900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>57200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>48000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>66500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>52600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>40600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>33400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>34500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>34800</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1189300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1132600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1046000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1037300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1032100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1106200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1105500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1172500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1181100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1292300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1320500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1344100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1149500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1008200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>833100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>683800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>607600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>654000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>598500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>594300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>588900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>581900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>484000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>446400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>437500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>471000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>403800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>432400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>426700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>428000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>395600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>367500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>316500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>293700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>301600</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>7800</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4241,201 +4340,207 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>53300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>56500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>49300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>43400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>40800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>49500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>42700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>40200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>28300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>23400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>19200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>21600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>20400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>21100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>27700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>23300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>15900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>16600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>12100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>11100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>8200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>7500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>7600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>9500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>7500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1531500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1492400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1388900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1342200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1256100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1316600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1336100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1335500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1328500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1457500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1497100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1511300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1322500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1273300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1294200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1165400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1061900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1040500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>974000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>830000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>951000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>701500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>643700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>564000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>527400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>559500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>486800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>502300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>486400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>503200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>456300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>416100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>359900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>336200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>343800</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
@@ -4455,8 +4560,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4533,165 +4638,171 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3392700</v>
+      </c>
+      <c r="E48" s="3">
         <v>3117800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3110600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3043100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2969100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2912500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2869100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2701200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2576500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2463700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2321500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2263500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2144500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2032800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1918300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1782400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1558800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1495700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1396900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1354900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1338600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1278500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1169000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1102700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>998000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>328400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>300300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>271500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>245400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>221000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>200400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>183600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>163800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>150500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>135500</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>407200</v>
+      </c>
+      <c r="E49" s="3">
         <v>408100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>409100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>410000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>410900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>411800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>412700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>414600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>407100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>407800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>406300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>407100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>407300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>407400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>408200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>408900</v>
-      </c>
-      <c r="S49" s="3">
-        <v>336700</v>
       </c>
       <c r="T49" s="3">
         <v>336700</v>
@@ -4709,7 +4820,7 @@
         <v>336700</v>
       </c>
       <c r="Y49" s="3">
-        <v>336800</v>
+        <v>336700</v>
       </c>
       <c r="Z49" s="3">
         <v>336800</v>
@@ -4747,8 +4858,11 @@
       <c r="AK49" s="3">
         <v>336800</v>
       </c>
+      <c r="AL49" s="3">
+        <v>336800</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4854,8 +4968,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4961,115 +5078,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E52" s="3">
         <v>13800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>22200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>19800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>19200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>17100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>7700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>7800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>7600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5175,115 +5298,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5368300</v>
+      </c>
+      <c r="E54" s="3">
         <v>5050500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4932200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4818100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4658700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4662600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4638100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4475500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4335200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4351200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4244700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4199400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3893400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3730700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3628100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3364300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2964700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2880400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2714400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2528700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2633900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2324300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2156900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2011100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1873400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1234100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1131900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1118400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1075900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1068000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1000900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>944200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>868400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>831200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>820400</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5321,8 +5450,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5360,186 +5490,190 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>814400</v>
+      </c>
+      <c r="E57" s="3">
         <v>794900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>737800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>698700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>641200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>679300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>706300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>664700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>572500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>590900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>642100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>770200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>688500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>661900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>634300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>529200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>402100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>417900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>362500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>326000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>319800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>368500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>318400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>272700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>229500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>313500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>237800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>265000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>255000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>258700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>249200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>243600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>205900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>158500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>165800</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>147200</v>
+      </c>
+      <c r="E58" s="3">
         <v>140700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>136700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>134900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>131300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>128500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>127500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>121100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>115900</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2100</v>
       </c>
       <c r="M58" s="3">
         <v>2100</v>
       </c>
       <c r="N58" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="O58" s="3">
         <v>1600</v>
       </c>
       <c r="P58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q58" s="3">
         <v>2100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1800</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
         <v>0</v>
       </c>
       <c r="Z58" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="3">
         <v>3500</v>
@@ -5572,438 +5706,453 @@
         <v>3500</v>
       </c>
       <c r="AK58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AL58" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E59" s="3">
         <v>96700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>76400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>77400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>99500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>75800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>82500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>87500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>413800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>417200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>425500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>403300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>368000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>376100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>325500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>268700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>279300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>253700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>205100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>184900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>184100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>174100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>148400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>165400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>87300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>82900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>66800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>72600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>97100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>91500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>75300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>83800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>81700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1253500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1244200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1193000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1149200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1073600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1152000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1174400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1116200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1006500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1006800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1061400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1197300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1093300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1032000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1012000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>860200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>673000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>698800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>618900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>533700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>506500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>552500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>492400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>424600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>398300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>404300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>324200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>335300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>331100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>359300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>344200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>322400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>293200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>243700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1806300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1545800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1563100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1556900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1532600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1496700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1520300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1507100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1553300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>405600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>371900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>264200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>195700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>195800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>195900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>195400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>195500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>207200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>206800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>207000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>413300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>142600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>143300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>140500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>143300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>141800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>142500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>156800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>169800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>185600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>183900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>178300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>351200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>387200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>157600</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E62" s="3">
         <v>22500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1281800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1228800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1243700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1202000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1179700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1155300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1129000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1015500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>977000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>957200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>937600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>904800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>864800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>798100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>775100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>711800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>103700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>101500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>91600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>87400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>80300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>84600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>82300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>77800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>65900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6109,8 +6258,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6216,8 +6368,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6323,115 +6478,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3146500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2880300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2821200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2771500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2677900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2731600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2752600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2665700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2606800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2694100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2662000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2705100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2491000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2407500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2363200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2184700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1884000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1883000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1782900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1678200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1824600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1560000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1433800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1340200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1253400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>649800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>568200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>583700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>588300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>625100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>612800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>583100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>722200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>696900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>479100</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6469,8 +6630,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6576,8 +6738,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6683,8 +6848,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6790,8 +6958,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6897,115 +7068,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1671200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1622300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1574800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1523100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1466400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1416400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1379300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1313400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1241900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1170400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1101200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1025000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>943200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>872200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>822400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>747700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>664800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>589000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>531900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>463100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>431100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>394000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>358700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>317700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>274100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>243600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>225700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>199100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>159200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>119600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>71600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>48300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>27900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>16800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7111,8 +7288,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7218,8 +7398,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7325,115 +7508,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2221800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2170200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2111100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2046600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1980800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1931000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1885500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1809800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1728400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1657200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1582600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1494300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1402400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1323200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1264900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1179600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1080700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>997400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>931500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>850500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>809300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>764300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>723000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>670900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>620000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>584300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>563700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>534700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>487600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>442900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>388200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>361100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>146100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>134300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>341400</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7539,227 +7728,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45743</v>
+      </c>
+      <c r="E80" s="2">
         <v>45652</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45470</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45379</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45288</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45197</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45106</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45015</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44924</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44833</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44560</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44378</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44287</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44098</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44007</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43916</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43825</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43734</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43643</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43552</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43461</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43370</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43279</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43188</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43097</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43006</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42915</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42824</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42733</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E81" s="3">
         <v>47500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>51700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>56700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>50000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>37100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>65900</v>
-      </c>
-      <c r="J81" s="3">
-        <v>71500</v>
       </c>
       <c r="K81" s="3">
         <v>71500</v>
       </c>
       <c r="L81" s="3">
+        <v>71500</v>
+      </c>
+      <c r="M81" s="3">
         <v>69200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>76200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>81800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>71000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>49900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>74600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>82900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>75800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>57100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>68800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>32000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>37100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>35300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>41000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>43600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>30700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>17900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>26600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>39800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>31900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>48000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>23300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>20400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>16700</v>
       </c>
-      <c r="AK81" s="3" t="s">
+      <c r="AL81" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7797,115 +7995,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E83" s="3">
         <v>51400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>50900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>49700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>46400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>39200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>40100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>38000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>34600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>42300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>40100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>38000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>34600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>33700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>30400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>27700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>26400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>24400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>22900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>22300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>22100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>20700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>18400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>17700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>17200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>14900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>13400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>11500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>10400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>9600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>9100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>8300</v>
       </c>
-      <c r="AK83" s="3" t="s">
+      <c r="AL83" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8011,8 +8213,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8118,8 +8323,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8225,8 +8433,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8332,8 +8543,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8439,115 +8653,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>71200</v>
+      </c>
+      <c r="E89" s="3">
         <v>101400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>160300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>194000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>147500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>104600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>222300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>226400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>250300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>105100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>11200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-63600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>108300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>155600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>101000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>136500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>173000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>72000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>24700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>87400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>95100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>27000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>41900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>59800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>43300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>40600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>26300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>16400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>10400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>56100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>18500</v>
       </c>
-      <c r="AK89" s="3" t="s">
+      <c r="AL89" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8585,115 +8805,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-97500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-123700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-113900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-111700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-133900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-134500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-139800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-139400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-133800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-108500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-113400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-130000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-145600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-86200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-45900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-102800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-43700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-27600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-38400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-55000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-62800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-46500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-42000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-35600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-27800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-24100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-19800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AK91" s="3" t="s">
+      <c r="AL91" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8799,8 +9023,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8906,115 +9133,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-97500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-123700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-113900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-111700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-133900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-134700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-156900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-139400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-136500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-108500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-109200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-101400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-130000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-145800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-149600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-45900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-102800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-43700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-27600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-38400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-55000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-62800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-46500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-31600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-46000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-27800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-32600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-25700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-22400</v>
       </c>
-      <c r="AK94" s="3" t="s">
+      <c r="AL94" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9052,8 +9285,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9081,8 +9315,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9159,8 +9393,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9266,8 +9503,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9373,8 +9613,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9480,115 +9723,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E100" s="3">
         <v>3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-30100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-70300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-115600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>33400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>110600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>72400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>7400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-199900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>276600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>8100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>4400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-13800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>6300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>7900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>15300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-36300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>4000</v>
       </c>
-      <c r="AK100" s="3" t="s">
+      <c r="AL100" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9616,8 +9865,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9694,89 +9943,92 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
         <v>6900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>42700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>80600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>23000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-27200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>57500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-25700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-107600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-190600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-36000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>12000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>46300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>36600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>136700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-155500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>262900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-57100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>32700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>51000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>100</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
       <c r="AD102" s="3">
         <v>0</v>
       </c>
@@ -9787,18 +10039,21 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-100</v>
       </c>
-      <c r="AI102" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>100</v>
       </c>
-      <c r="AK102" s="3" t="s">
+      <c r="AL102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
   <si>
     <t>FND</t>
   </si>
@@ -656,491 +656,504 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45834</v>
+      </c>
+      <c r="E7" s="2">
         <v>45743</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45652</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45470</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45379</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45288</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45197</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45106</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45015</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44924</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44833</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44560</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44378</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44287</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44098</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44007</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43825</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43734</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43643</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43552</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43461</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43370</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43279</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43188</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43097</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43006</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42915</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42824</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42733</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1214200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1160700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1107400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1117900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1133100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1097300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1048100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1107800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1135900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1122100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1048100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1097800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1089800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1028700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>914300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>876600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>860100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>782500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>723700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>684800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>462400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>554900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>527000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>521100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>520300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>477100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>436700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>435900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>434300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>402900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>389500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>343900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>344000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>307300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>278300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>271300</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>666600</v>
+      </c>
+      <c r="E9" s="3">
         <v>641400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>619200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>625400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>635300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>620200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>599800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>633500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>650700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>646200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>612200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>650300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>653600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>620700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>559700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>511200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>494700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>445600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>416100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>390200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>265700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>318900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>297000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>307300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>302500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>275700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>255700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>257700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>256600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>237600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>227100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>201400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>201800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>181800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>163500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>160300</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>547600</v>
+      </c>
+      <c r="E10" s="3">
         <v>519300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>488200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>492500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>497900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>477100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>448400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>474300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>485200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>475800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>435900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>447500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>436200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>408000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>354600</v>
-      </c>
-      <c r="R10" s="3">
-        <v>365400</v>
       </c>
       <c r="S10" s="3">
         <v>365400</v>
       </c>
       <c r="T10" s="3">
+        <v>365400</v>
+      </c>
+      <c r="U10" s="3">
         <v>336900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>307600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>294600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>196700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>236000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>230000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>213800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>217800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>201400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>181000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>178200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>177700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>165300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>162400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>142500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>142200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>125500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>114800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1179,8 +1192,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1289,8 +1303,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1399,43 +1416,46 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-6800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-700</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>1400</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1443,35 +1463,35 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>1700</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-1000</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1479,8 +1499,8 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1488,29 +1508,32 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL14" s="3">
         <v>1700</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1518,32 +1541,32 @@
         <v>60000</v>
       </c>
       <c r="E15" s="3">
+        <v>60000</v>
+      </c>
+      <c r="F15" s="3">
         <v>59800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>57900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>58400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>56400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>54900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>50900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>49700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>46400</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1619,8 +1642,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1656,228 +1682,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1132300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1096900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1055000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1051600</v>
       </c>
-      <c r="G17" s="3">
-        <v>1062500</v>
-      </c>
       <c r="H17" s="3">
+        <v>1061800</v>
+      </c>
+      <c r="I17" s="3">
         <v>1037400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1001100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1023000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1040900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1025100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>953300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>996200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>983400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>934800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>853200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>793200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>763300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>686600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>655600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>606000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>440200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>508300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>484900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>489700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>474400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>437300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>413400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>401600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>397000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>366400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>357100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>315300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>315400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>284600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>260000</v>
       </c>
-      <c r="AL17" s="3" t="s">
+      <c r="AM17" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>81900</v>
+      </c>
+      <c r="E18" s="3">
         <v>63900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>52400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>66300</v>
       </c>
-      <c r="G18" s="3">
-        <v>70700</v>
-      </c>
       <c r="H18" s="3">
+        <v>71300</v>
+      </c>
+      <c r="I18" s="3">
         <v>59900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>47100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>84800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>95000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>97000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>94800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>101600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>106400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>93900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>61100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>83400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>96800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>95900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>68100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>78800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>22200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>46600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>42100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>31400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>45900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>39800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>23300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>34300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>37300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>36500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>32400</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>28600</v>
       </c>
       <c r="AI18" s="3">
         <v>28600</v>
       </c>
       <c r="AJ18" s="3">
+        <v>28600</v>
+      </c>
+      <c r="AK18" s="3">
         <v>22700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>18300</v>
       </c>
-      <c r="AL18" s="3" t="s">
+      <c r="AM18" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1916,8 +1949,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1948,8 +1982,8 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1967,11 +2001,11 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>900</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1994,11 +2028,11 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -2023,451 +2057,466 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
-      <c r="AL20" s="3" t="s">
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>141900</v>
+      </c>
+      <c r="E21" s="3">
         <v>123800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>112200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>124200</v>
       </c>
-      <c r="G21" s="3">
-        <v>129000</v>
-      </c>
       <c r="H21" s="3">
+        <v>129700</v>
+      </c>
+      <c r="I21" s="3">
         <v>116300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>102000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>135700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>144700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>143300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>137100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>141800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>144400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>128600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>94800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>113800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>125400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>122400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>92400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>101700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>44400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>68800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>62800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>49800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>63600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>56900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>38300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>47600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>49300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>48000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>42800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>38200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>37800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>31600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>26600</v>
       </c>
-      <c r="AL21" s="3" t="s">
+      <c r="AM21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E22" s="3">
         <v>3100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>-1900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I22" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J22" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="K22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="L22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="M22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="N22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="O22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P22" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1200</v>
-      </c>
-      <c r="H22" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I22" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="J22" s="3">
-        <v>2600</v>
-      </c>
-      <c r="K22" s="3">
-        <v>4100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>4900</v>
-      </c>
-      <c r="M22" s="3">
-        <v>5300</v>
-      </c>
-      <c r="N22" s="3">
-        <v>3000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1700</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1100</v>
       </c>
       <c r="R22" s="3">
         <v>1100</v>
       </c>
       <c r="S22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>2400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>2600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>3400</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>5400</v>
       </c>
       <c r="AK22" s="3">
         <v>5400</v>
       </c>
       <c r="AL22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AM22" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E23" s="3">
         <v>62700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>59300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>66100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>70700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>57400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>45300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>83500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>92100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>90700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>89400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>98600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>104700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>92800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>60000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>82300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>97300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>94600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>65800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>76800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>19800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>44900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>40400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>29400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>43700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>36800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>20500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>32100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>35100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>34700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>30000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>26000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>25300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>17300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>12900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E24" s="3">
         <v>13800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>17600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>20600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>20200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>22500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>22900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>21900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>14300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>18800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-12200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-11600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-4700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>6100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-3800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2576,228 +2625,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E26" s="3">
         <v>48900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>47500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>51700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>56700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>50000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>37100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>65900</v>
-      </c>
-      <c r="K26" s="3">
-        <v>71500</v>
       </c>
       <c r="L26" s="3">
         <v>71500</v>
       </c>
       <c r="M26" s="3">
+        <v>71500</v>
+      </c>
+      <c r="N26" s="3">
         <v>69200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>76200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>81800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>71000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>49900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>74600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>82900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>75800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>57100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>68800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>32000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>37100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>35300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>41000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>43600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>30700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>17300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>26000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>39800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>31900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>30100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>23300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>11100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>16700</v>
       </c>
-      <c r="AL26" s="3" t="s">
+      <c r="AM26" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E27" s="3">
         <v>48900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>47500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>51700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>56700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>50000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>37100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>65900</v>
-      </c>
-      <c r="K27" s="3">
-        <v>71500</v>
       </c>
       <c r="L27" s="3">
         <v>71500</v>
       </c>
       <c r="M27" s="3">
+        <v>71500</v>
+      </c>
+      <c r="N27" s="3">
         <v>69200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>76200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>81800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>71000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>49900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>74600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>82900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>75800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>57100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>68800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>32000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>37100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>35300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>41000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>43600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>30700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>17300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>26000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>39800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>31900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>30100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>23300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>11100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>16700</v>
       </c>
-      <c r="AL27" s="3" t="s">
+      <c r="AM27" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2906,8 +2964,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2968,17 +3029,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2986,24 +3047,24 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>600</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>600</v>
       </c>
       <c r="AE29" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>17800</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3016,8 +3077,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3126,8 +3190,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3236,8 +3303,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3268,8 +3338,8 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -3287,11 +3357,11 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-900</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -3314,11 +3384,11 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
@@ -3343,121 +3413,127 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
-      <c r="AL32" s="3" t="s">
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E33" s="3">
         <v>48900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>47500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>51700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>56700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>50000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>37100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>65900</v>
-      </c>
-      <c r="K33" s="3">
-        <v>71500</v>
       </c>
       <c r="L33" s="3">
         <v>71500</v>
       </c>
       <c r="M33" s="3">
+        <v>71500</v>
+      </c>
+      <c r="N33" s="3">
         <v>69200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>76200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>81800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>71000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>49900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>74600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>82900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>75800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>57100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>68800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>32000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>37100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>35300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>41000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>43600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>30700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>17900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>26600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>39800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>31900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>48000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>23300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>11100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>16700</v>
       </c>
-      <c r="AL33" s="3" t="s">
+      <c r="AM33" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3566,233 +3642,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E35" s="3">
         <v>48900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>47500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>51700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>56700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>50000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>37100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>65900</v>
-      </c>
-      <c r="K35" s="3">
-        <v>71500</v>
       </c>
       <c r="L35" s="3">
         <v>71500</v>
       </c>
       <c r="M35" s="3">
+        <v>71500</v>
+      </c>
+      <c r="N35" s="3">
         <v>69200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>76200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>81800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>71000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>49900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>74600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>82900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>75800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>57100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>68800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>32000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>37100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>35300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>41000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>43600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>30700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>17900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>26600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>39800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>31900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>48000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>23300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>11100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>16700</v>
       </c>
-      <c r="AL35" s="3" t="s">
+      <c r="AM35" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45834</v>
+      </c>
+      <c r="E38" s="2">
         <v>45743</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45652</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45470</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45379</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45288</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45197</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45106</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45015</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44924</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44833</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44560</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44378</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44287</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44098</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44007</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43825</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43734</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43643</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43552</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43461</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43370</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43279</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43188</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43097</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43006</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42915</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42824</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42733</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3831,8 +3916,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3871,97 +3957,98 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>176900</v>
+      </c>
+      <c r="E41" s="3">
         <v>186900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>187700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>180800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>138100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>57400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>34400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>61600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>31800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>139400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>330100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>366100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>354100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>307800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>271100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>134400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>289900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>27000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>84100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>51500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>600</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>500</v>
       </c>
       <c r="AE41" s="3">
         <v>500</v>
       </c>
       <c r="AF41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AG41" s="3">
         <v>600</v>
@@ -3970,19 +4057,22 @@
         <v>600</v>
       </c>
       <c r="AI41" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AJ41" s="3">
         <v>400</v>
       </c>
       <c r="AK41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AL41" s="3">
         <v>500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4002,11 +4092,11 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>1800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -4091,240 +4181,249 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>112800</v>
+      </c>
+      <c r="E43" s="3">
         <v>105500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>115400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>107700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>113400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>116800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>127400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>113900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>102300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>88000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>102100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>112400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>111700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>97800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>85000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>81500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>72800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>60000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>50400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>81000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>82100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>50600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>72200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>54500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>38500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>66100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>71900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>65900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>57200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>48000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>66500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>52600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>40600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>33400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>34500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>34800</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1211400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1189300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1132600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1046000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1037300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1032100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1106200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1105500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1172500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1181100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1292300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1320500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1344100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1149500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1008200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>833100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>683800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>607600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>654000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>598500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>594300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>588900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>581900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>484000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>446400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>437500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>471000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>403800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>432400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>426700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>428000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>395600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>367500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>316500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>293700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>301600</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>7800</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4343,207 +4442,213 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>53300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>56500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>49300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>43400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>40800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>49500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>42700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>40200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>28300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>23400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>19200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>21600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>20400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>21100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>27700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>23300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>15900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>16600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>12100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>11100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>8200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>7500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>7600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>9500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>7500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1553200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1531500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1492400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1388900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1342200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1256100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1316600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1336100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1335500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1328500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1457500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1497100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1511300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1322500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1273300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1294200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1165400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1061900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1040500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>974000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>830000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>951000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>701500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>643700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>564000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>527400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>559500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>486800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>502300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>486400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>503200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>456300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>416100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>359900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>336200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>343800</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
@@ -4563,8 +4668,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4641,171 +4746,177 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3407800</v>
+      </c>
+      <c r="E48" s="3">
         <v>3392700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3117800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3110600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3043100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2969100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2912500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2869100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2701200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2576500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2463700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2321500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2263500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2144500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2032800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1918300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1782400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1558800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1495700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1396900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1354900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1338600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1278500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1169000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1102700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>998000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>328400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>300300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>271500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>245400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>221000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>200400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>183600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>163800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>150500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>135500</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>406300</v>
+      </c>
+      <c r="E49" s="3">
         <v>407200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>408100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>409100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>410000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>410900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>411800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>412700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>414600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>407100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>407800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>406300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>407100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>407300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>407400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>408200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>408900</v>
-      </c>
-      <c r="T49" s="3">
-        <v>336700</v>
       </c>
       <c r="U49" s="3">
         <v>336700</v>
@@ -4823,7 +4934,7 @@
         <v>336700</v>
       </c>
       <c r="Z49" s="3">
-        <v>336800</v>
+        <v>336700</v>
       </c>
       <c r="AA49" s="3">
         <v>336800</v>
@@ -4861,8 +4972,11 @@
       <c r="AL49" s="3">
         <v>336800</v>
       </c>
+      <c r="AM49" s="3">
+        <v>336800</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4971,8 +5085,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5081,118 +5198,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E52" s="3">
         <v>19600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>22200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>19800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>19200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>7400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>7700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>7800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>7600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5301,118 +5424,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5411200</v>
+      </c>
+      <c r="E54" s="3">
         <v>5368300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5050500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4932200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4818100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4658700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4662600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4638100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4475500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4335200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4351200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4244700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4199400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3893400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3730700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3628100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3364300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2964700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2880400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2714400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2528700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2633900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2324300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2156900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2011100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1873400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1234100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1131900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1118400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1075900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1068000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1000900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>944200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>868400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>831200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>820400</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5451,8 +5580,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5491,192 +5621,196 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>777100</v>
+      </c>
+      <c r="E57" s="3">
         <v>814400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>794900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>737800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>698700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>641200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>679300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>706300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>664700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>572500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>590900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>642100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>770200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>688500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>661900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>634300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>529200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>402100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>417900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>362500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>326000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>319800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>368500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>318400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>272700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>229500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>313500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>237800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>265000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>255000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>258700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>249200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>243600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>205900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>158500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>165800</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E58" s="3">
         <v>147200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>140700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>136700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>134900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>131300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>128500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>127500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>121100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>115900</v>
-      </c>
-      <c r="M58" s="3">
-        <v>2100</v>
       </c>
       <c r="N58" s="3">
         <v>2100</v>
       </c>
       <c r="O58" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="P58" s="3">
         <v>1600</v>
       </c>
       <c r="Q58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R58" s="3">
         <v>2100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1800</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
       <c r="AA58" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="AB58" s="3">
         <v>3500</v>
@@ -5709,450 +5843,465 @@
         <v>3500</v>
       </c>
       <c r="AL58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AM58" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E59" s="3">
         <v>23100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>96700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>76400</v>
       </c>
-      <c r="G59" s="3">
-        <v>17500</v>
-      </c>
       <c r="H59" s="3">
+        <v>77500</v>
+      </c>
+      <c r="I59" s="3">
         <v>77400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>99500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>75800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>82500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>87500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>413800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>417200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>425500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>403300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>368000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>376100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>325500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>268700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>279300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>253700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>205100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>184900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>184100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>174100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>148400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>165400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>87300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>82900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>66800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>72600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>97100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>91500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>75300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>83800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>81700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1237800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1253500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1244200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1193000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1149200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1073600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1152000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1174400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1116200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1006500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1006800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1061400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1197300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1093300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1032000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1012000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>860200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>673000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>698800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>618900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>533700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>506500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>552500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>492400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>424600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>398300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>404300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>324200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>335300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>331100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>359300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>344200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>322400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>293200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>243700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1800900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1806300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1545800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1563100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1556900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1532600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1496700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1520300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1507100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1553300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>405600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>371900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>264200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>195700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>195800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>195900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>195400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>195500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>207200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>206800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>207000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>413300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>142600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>143300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>140500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>143300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>141800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>142500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>156800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>169800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>185600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>183900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>178300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>351200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>387200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>157600</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E62" s="3">
         <v>23900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>22500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1281800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1228800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1243700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1202000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1179700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1155300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1129000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1015500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>977000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>957200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>937600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>904800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>864800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>798100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>775100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>711800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>103700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>101500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>91600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>87400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>80300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>84600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>82300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>77800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>65900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6261,8 +6410,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6371,8 +6523,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6481,118 +6636,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3116900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3146500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2880300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2821200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2771500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2677900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2731600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2752600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2665700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2606800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2694100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2662000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2705100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2491000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2407500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2363200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2184700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1884000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1883000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1782900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1678200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1824600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1560000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1433800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1340200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1253400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>649800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>568200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>583700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>588300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>625100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>612800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>583100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>722200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>696900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>479100</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6631,8 +6792,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6741,8 +6903,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6851,8 +7016,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6961,8 +7129,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7071,118 +7242,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1734300</v>
+      </c>
+      <c r="E72" s="3">
         <v>1671200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1622300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1574800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1523100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1466400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1416400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1379300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1313400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1241900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1170400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1101200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1025000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>943200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>872200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>822400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>747700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>664800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>589000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>531900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>463100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>431100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>394000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>358700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>317700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>274100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>243600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>225700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>199100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>159200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>119600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>71600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>48300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>27900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>16800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7291,8 +7468,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7401,8 +7581,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7511,118 +7694,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2294300</v>
+      </c>
+      <c r="E76" s="3">
         <v>2221800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2170200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2111100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2046600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1980800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1931000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1885500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1809800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1728400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1657200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1582600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1494300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1402400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1323200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1264900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1179600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1080700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>997400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>931500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>850500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>809300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>764300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>723000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>670900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>620000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>584300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>563700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>534700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>487600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>442900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>388200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>361100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>146100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>134300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>341400</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7731,233 +7920,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45834</v>
+      </c>
+      <c r="E80" s="2">
         <v>45743</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45652</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45470</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45379</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45288</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45197</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45106</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45015</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44924</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44833</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44560</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44378</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44287</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44098</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44007</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43825</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43734</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43643</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43552</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43461</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43370</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43279</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43188</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43097</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43006</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42915</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42824</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42733</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E81" s="3">
         <v>48900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>47500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>51700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>56700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>50000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>37100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>65900</v>
-      </c>
-      <c r="K81" s="3">
-        <v>71500</v>
       </c>
       <c r="L81" s="3">
         <v>71500</v>
       </c>
       <c r="M81" s="3">
+        <v>71500</v>
+      </c>
+      <c r="N81" s="3">
         <v>69200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>76200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>81800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>71000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>49900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>74600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>82900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>75800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>57100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>68800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>32000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>37100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>35300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>41000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>43600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>30700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>17900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>26600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>39800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>31900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>48000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>23300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>11100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>16700</v>
       </c>
-      <c r="AL81" s="3" t="s">
+      <c r="AM81" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7996,118 +8194,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E83" s="3">
         <v>56400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>51400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>50900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>49700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>46400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>39200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>40100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>38000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>34600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>42300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>40100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>38000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>34600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>33700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>30400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>27700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>26400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>24400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>22900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>22300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>22100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>20700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>18400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>17700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>17200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>14900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>13400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>12100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>11500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>10400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>9600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>8900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>8300</v>
       </c>
-      <c r="AL83" s="3" t="s">
+      <c r="AM83" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8216,8 +8418,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8326,8 +8531,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8436,8 +8644,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8546,8 +8757,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8656,118 +8870,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>84100</v>
+      </c>
+      <c r="E89" s="3">
         <v>71200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>101400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>160300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>194000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>147500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>104600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>222300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>226400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>250300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>105100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-63600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>108300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>155600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>101000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>136500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>173000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>72000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>24700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>87400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>95100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>27000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>41900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>59800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>43300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>40600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>26300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>16400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>10400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>56100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>18500</v>
       </c>
-      <c r="AL89" s="3" t="s">
+      <c r="AM89" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8806,118 +9026,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-94100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-66700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-97500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-123700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-113900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-111700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-133900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-134500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-139800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-139400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-133800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-108500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-113400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-130000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-145600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-86200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-45900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-102800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-43700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-27600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-38400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-55000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-62800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-46500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-42000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-35600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-27800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-24100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-19800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AL91" s="3" t="s">
+      <c r="AM91" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9026,8 +9250,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9136,118 +9363,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-94100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-66700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-97500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-123700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-113900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-111700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-133900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-134700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-156900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-139400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-136500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-108500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-109200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-101400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-130000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-145800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-149600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-45900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-102800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-43700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-27600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-38400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-55000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-46500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-31600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-46000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-27800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-32600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-25700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-22400</v>
       </c>
-      <c r="AL94" s="3" t="s">
+      <c r="AM94" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9286,8 +9519,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9318,8 +9552,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9396,8 +9630,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9506,8 +9743,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9616,8 +9856,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9726,118 +9969,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-30100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-70300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-115600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>33400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>110600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>72400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>6000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-8800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>7400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-199900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>276600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>8100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-13800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-7700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>6300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>7900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>15300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-36300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>4000</v>
       </c>
-      <c r="AL100" s="3" t="s">
+      <c r="AM100" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9868,8 +10117,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9946,92 +10195,95 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>42700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>80600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>23000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-27200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>57500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-25700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-107600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-190600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-36000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>12000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>46300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>36600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>136700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-155500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>262900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-57100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>32700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>51000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>100</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
       <c r="AE102" s="3">
         <v>0</v>
       </c>
@@ -10042,18 +10294,21 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ102" s="3">
-        <v>0</v>
-      </c>
       <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3">
         <v>100</v>
       </c>
-      <c r="AL102" s="3" t="s">
+      <c r="AM102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>FND</t>
   </si>
@@ -656,517 +656,529 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46016</v>
+      </c>
+      <c r="E7" s="2">
         <v>45925</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45743</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45652</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45561</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45470</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45379</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45288</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45197</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45106</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45015</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44924</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44833</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44560</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44378</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44287</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44098</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44007</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43916</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43825</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43734</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43643</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43552</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43461</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43370</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43279</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43188</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43097</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43006</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42915</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42824</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42733</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1129700</v>
+      </c>
+      <c r="E8" s="3">
         <v>1179500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1214200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1160700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1107400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1117900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1133100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1097300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1048100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1107800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1135900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1122100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1048100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1097800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1089800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1028700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>914300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>876600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>860100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>782500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>723700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>684800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>462400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>554900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>527000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>521100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>520300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>477100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>436700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>435900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>434300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>402900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>389500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>343900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>344000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>307300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>278300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>271300</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>623100</v>
+      </c>
+      <c r="E9" s="3">
         <v>652500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>666600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>641400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>619200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>625400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>635300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>620200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>599800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>633500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>650700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>646200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>612200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>650300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>653600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>620700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>559700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>511200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>494700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>445600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>416100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>390200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>265700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>318900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>297000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>307300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>302500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>275700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>255700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>257700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>256600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>237600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>227100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>201400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>201800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>181800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>163500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>160300</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>506600</v>
+      </c>
+      <c r="E10" s="3">
         <v>527100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>547600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>519300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>488200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>492500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>497900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>477100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>448400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>474300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>485200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>475800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>435900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>447500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>436200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>408000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>354600</v>
-      </c>
-      <c r="T10" s="3">
-        <v>365400</v>
       </c>
       <c r="U10" s="3">
         <v>365400</v>
       </c>
       <c r="V10" s="3">
+        <v>365400</v>
+      </c>
+      <c r="W10" s="3">
         <v>336900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>307600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>294600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>196700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>236000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>230000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>213800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>217800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>201400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>181000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>178200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>177700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>165300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>162400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>142500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>142200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>125500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>114800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1323,8 +1336,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1439,49 +1455,52 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>-400</v>
       </c>
-      <c r="G14" s="3">
-        <v>-6800</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>900</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>1400</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1489,35 +1508,35 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>1700</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1525,8 +1544,8 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1534,68 +1553,71 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>5400</v>
       </c>
-      <c r="AL14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM14" s="3">
+      <c r="AM14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN14" s="3">
         <v>1700</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E15" s="3">
         <v>60500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>60000</v>
       </c>
       <c r="F15" s="3">
         <v>60000</v>
       </c>
       <c r="G15" s="3">
+        <v>60000</v>
+      </c>
+      <c r="H15" s="3">
         <v>59800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>57900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>58400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>56400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>54900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>50900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>49700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>46400</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1671,8 +1693,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,240 +1735,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1077700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1107500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1132300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1096900</v>
       </c>
-      <c r="G17" s="3">
-        <v>1055000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1048200</v>
+      </c>
+      <c r="I17" s="3">
         <v>1051600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1061800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1037400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1001100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1023000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1040900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1025100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>953300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>996200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>983400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>934800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>853200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>793200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>763300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>686600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>655600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>606000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>440200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>508300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>484900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>489700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>474400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>437300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>413400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>401600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>397000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>366400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>357100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>315300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>315400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>284600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>260000</v>
       </c>
-      <c r="AN17" s="3" t="s">
+      <c r="AO17" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E18" s="3">
         <v>72000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>81900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>63900</v>
       </c>
-      <c r="G18" s="3">
-        <v>52400</v>
-      </c>
       <c r="H18" s="3">
+        <v>59200</v>
+      </c>
+      <c r="I18" s="3">
         <v>66300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>71300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>59900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>47100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>84800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>95000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>97000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>94800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>101600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>106400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>93900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>61100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>83400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>96800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>95900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>68100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>78800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>22200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>46600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>42100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>31400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>45900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>39800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>23300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>34300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>37300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>36500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>32400</v>
-      </c>
-      <c r="AJ18" s="3">
-        <v>28600</v>
       </c>
       <c r="AK18" s="3">
         <v>28600</v>
       </c>
       <c r="AL18" s="3">
+        <v>28600</v>
+      </c>
+      <c r="AM18" s="3">
         <v>22700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>18300</v>
       </c>
-      <c r="AN18" s="3" t="s">
+      <c r="AO18" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1984,8 +2016,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2022,8 +2055,8 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -2041,11 +2074,11 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>900</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -2068,11 +2101,11 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
@@ -2097,127 +2130,133 @@
       <c r="AM20" s="3">
         <v>0</v>
       </c>
-      <c r="AN20" s="3" t="s">
+      <c r="AN20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>112600</v>
+      </c>
+      <c r="E21" s="3">
         <v>132600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>141900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>123800</v>
       </c>
-      <c r="G21" s="3">
-        <v>112200</v>
-      </c>
       <c r="H21" s="3">
+        <v>119000</v>
+      </c>
+      <c r="I21" s="3">
         <v>124200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>129700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>116300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>102000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>135700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>144700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>143300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>137100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>141800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>144400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>128600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>94800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>113800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>125400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>122400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>92400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>101700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>44400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>68800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>62800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>49800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>63600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>56900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>38300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>47600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>49300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>48000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>42800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>38200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>37800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>31600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>26600</v>
       </c>
-      <c r="AN21" s="3" t="s">
+      <c r="AO21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2225,347 +2264,356 @@
         <v>2600</v>
       </c>
       <c r="E22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F22" s="3">
         <v>3000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3100</v>
       </c>
-      <c r="G22" s="3">
-        <v>-1900</v>
-      </c>
       <c r="H22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I22" s="3">
         <v>2200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>-2800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>5300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1200</v>
-      </c>
-      <c r="S22" s="3">
-        <v>1100</v>
       </c>
       <c r="T22" s="3">
         <v>1100</v>
       </c>
       <c r="U22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>2100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>2600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>3400</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>5400</v>
       </c>
       <c r="AM22" s="3">
         <v>5400</v>
       </c>
       <c r="AN22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AO22" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E23" s="3">
         <v>71400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>80800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>62700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>59300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>66100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>70700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>57400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>45300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>83500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>92100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>90700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>89400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>98600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>104700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>92800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>60000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>82300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>97300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>94600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>65800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>76800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>19800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>44900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>40400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>29400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>43700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>36800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>20500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>32100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>35100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>34700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>30000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>26000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>25300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>17300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>12900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E24" s="3">
         <v>14200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>17600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>17600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>20600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>19100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>20200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>22500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>22900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>21900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>10100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>14300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>18800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>8600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-11600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-4700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>4900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>6100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-3800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2680,240 +2728,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E26" s="3">
         <v>57300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>63200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>48900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>47500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>51700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>56700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>50000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>37100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>65900</v>
-      </c>
-      <c r="M26" s="3">
-        <v>71500</v>
       </c>
       <c r="N26" s="3">
         <v>71500</v>
       </c>
       <c r="O26" s="3">
+        <v>71500</v>
+      </c>
+      <c r="P26" s="3">
         <v>69200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>76200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>81800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>71000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>49900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>74600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>82900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>75800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>57100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>68800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>32000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>37100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>35300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>41000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>43600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>30700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>17300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>26000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>39800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>31900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>30100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>23300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>20400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>11100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>16700</v>
       </c>
-      <c r="AN26" s="3" t="s">
+      <c r="AO26" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E27" s="3">
         <v>57300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>63200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>48900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>47500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>51700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>56700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>50000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>37100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>65900</v>
-      </c>
-      <c r="M27" s="3">
-        <v>71500</v>
       </c>
       <c r="N27" s="3">
         <v>71500</v>
       </c>
       <c r="O27" s="3">
+        <v>71500</v>
+      </c>
+      <c r="P27" s="3">
         <v>69200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>76200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>81800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>71000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>49900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>74600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>82900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>75800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>57100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>68800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>32000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>37100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>35300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>41000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>43600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>30700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>17300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>26000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>39800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>31900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>30100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>23300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>20400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>11100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>16700</v>
       </c>
-      <c r="AN27" s="3" t="s">
+      <c r="AO27" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3028,8 +3085,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3096,17 +3156,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -3114,24 +3174,24 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>600</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF29" s="3">
         <v>600</v>
       </c>
       <c r="AG29" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AH29" s="3">
         <v>0</v>
       </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>17800</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3144,8 +3204,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3260,8 +3323,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3376,8 +3442,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3414,8 +3483,8 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -3433,11 +3502,11 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-900</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -3460,11 +3529,11 @@
         <v>0</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
@@ -3489,127 +3558,133 @@
       <c r="AM32" s="3">
         <v>0</v>
       </c>
-      <c r="AN32" s="3" t="s">
+      <c r="AN32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E33" s="3">
         <v>57300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>63200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>48900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>47500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>51700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>56700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>50000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>37100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>65900</v>
-      </c>
-      <c r="M33" s="3">
-        <v>71500</v>
       </c>
       <c r="N33" s="3">
         <v>71500</v>
       </c>
       <c r="O33" s="3">
+        <v>71500</v>
+      </c>
+      <c r="P33" s="3">
         <v>69200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>76200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>81800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>71000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>49900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>74600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>82900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>75800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>57100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>68800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>32000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>37100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>35300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>41000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>43600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>30700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>17900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>26600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>39800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>31900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>48000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>23300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>20400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>11100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>16700</v>
       </c>
-      <c r="AN33" s="3" t="s">
+      <c r="AO33" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3724,245 +3799,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E35" s="3">
         <v>57300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>63200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>48900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>47500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>51700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>56700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>50000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>37100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>65900</v>
-      </c>
-      <c r="M35" s="3">
-        <v>71500</v>
       </c>
       <c r="N35" s="3">
         <v>71500</v>
       </c>
       <c r="O35" s="3">
+        <v>71500</v>
+      </c>
+      <c r="P35" s="3">
         <v>69200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>76200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>81800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>71000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>49900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>74600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>82900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>75800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>57100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>68800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>32000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>37100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>35300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>41000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>43600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>30700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>17900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>26600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>39800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>31900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>48000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>23300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>20400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>11100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>16700</v>
       </c>
-      <c r="AN35" s="3" t="s">
+      <c r="AO35" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46016</v>
+      </c>
+      <c r="E38" s="2">
         <v>45925</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45743</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45652</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45561</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45470</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45379</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45288</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45197</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45106</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45015</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44924</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44833</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44560</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44378</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44287</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44098</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44007</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43916</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43825</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43734</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43643</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43552</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43461</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43370</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43279</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43188</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43097</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43006</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42915</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42824</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42733</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4003,8 +4087,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4045,103 +4130,104 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>249300</v>
+      </c>
+      <c r="E41" s="3">
         <v>204500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>176900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>186900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>187700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>180800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>138100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>57400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>34400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>61600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>31800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>139400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>330100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>366100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>354100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>307800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>271100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>134400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>289900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>27000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>84100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>51500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>600</v>
-      </c>
-      <c r="AF41" s="3">
-        <v>500</v>
       </c>
       <c r="AG41" s="3">
         <v>500</v>
       </c>
       <c r="AH41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AI41" s="3">
         <v>600</v>
@@ -4150,19 +4236,22 @@
         <v>600</v>
       </c>
       <c r="AK41" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AL41" s="3">
         <v>400</v>
       </c>
       <c r="AM41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AN41" s="3">
         <v>500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4188,11 +4277,11 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>1800</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -4277,240 +4366,249 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>101300</v>
+      </c>
+      <c r="E43" s="3">
         <v>169600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>112800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>105500</v>
       </c>
-      <c r="G43" s="3">
-        <v>115400</v>
-      </c>
       <c r="H43" s="3">
+        <v>123200</v>
+      </c>
+      <c r="I43" s="3">
         <v>107700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>113400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>116800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>127400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>113900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>102300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>88000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>102100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>112400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>111700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>97800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>85000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>81500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>72800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>60000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>50400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>81000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>82100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>50600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>72200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>54500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>38500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>66100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>71900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>65900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>57200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>48000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>66500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>52600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>40600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>33400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>34500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>34800</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1133100</v>
+      </c>
+      <c r="E44" s="3">
         <v>1164200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1211400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1189300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1132600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1046000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1037300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1032100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1106200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1105500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1172500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1181100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1292300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1320500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1344100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1149500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1008200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>833100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>683800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>607600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>654000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>598500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>594300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>588900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>581900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>484000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>446400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>437500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>471000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>403800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>432400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>426700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>428000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>395600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>367500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>316500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>293700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>301600</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4523,8 +4621,8 @@
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
-        <v>7800</v>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
@@ -4547,202 +4645,208 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>53300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>56500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>49300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>43400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>40800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>49500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>42700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>40200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>28300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>23400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>19200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>21600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>20400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>21100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>27700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>23300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>15900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>16600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>12100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>11100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>7500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>7600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>9500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>7500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1527900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1594200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1553200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1531500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1492400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1388900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1342200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1256100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1316600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1336100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1335500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1328500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1457500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1497100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1511300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1322500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1273300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1294200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1165400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1061900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1040500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>974000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>830000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>951000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>701500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>643700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>564000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>527400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>559500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>486800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>502300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>486400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>503200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>456300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>416100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>359900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>336200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>343800</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4755,11 +4859,11 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
@@ -4779,8 +4883,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4857,183 +4961,189 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3473900</v>
+      </c>
+      <c r="E48" s="3">
         <v>3467400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3407800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3392700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3117800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3110600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3043100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2969100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2912500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2869100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2701200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2576500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2463700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2321500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2263500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2144500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2032800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1918300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1782400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1558800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1495700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1396900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1354900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1338600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1278500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1169000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1102700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>998000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>328400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>300300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>271500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>245400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>221000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>200400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>183600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>163800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>150500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>135500</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>404500</v>
+      </c>
+      <c r="E49" s="3">
         <v>405400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>406300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>407200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>408100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>409100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>410000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>410900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>411800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>412700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>414600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>407100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>407800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>406300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>407100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>407300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>407400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>408200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>408900</v>
-      </c>
-      <c r="V49" s="3">
-        <v>336700</v>
       </c>
       <c r="W49" s="3">
         <v>336700</v>
@@ -5051,7 +5161,7 @@
         <v>336700</v>
       </c>
       <c r="AB49" s="3">
-        <v>336800</v>
+        <v>336700</v>
       </c>
       <c r="AC49" s="3">
         <v>336800</v>
@@ -5089,8 +5199,11 @@
       <c r="AN49" s="3">
         <v>336800</v>
       </c>
+      <c r="AO49" s="3">
+        <v>336800</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5205,8 +5318,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5321,124 +5437,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E52" s="3">
         <v>35300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>22200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>19800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>19200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>11200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>7300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>7400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>7700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>7800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>7600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5553,124 +5675,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5469400</v>
+      </c>
+      <c r="E54" s="3">
         <v>5520800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5411200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5368300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5050500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4932200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4818100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4658700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4662600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4638100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4475500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4335200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4351200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4244700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4199400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3893400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3730700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3628100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3364300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2964700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2880400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2714400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2528700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2633900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2324300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2156900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2011100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1873400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1234100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1131900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1118400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1075900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1068000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1000900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>944200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>868400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>831200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>820400</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5711,8 +5839,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5753,204 +5882,208 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>683700</v>
+      </c>
+      <c r="E57" s="3">
         <v>724600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>777100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>814400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>794900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>737800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>698700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>641200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>679300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>706300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>664700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>572500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>590900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>642100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>770200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>688500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>661900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>634300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>529200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>402100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>417900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>362500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>326000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>319800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>368500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>318400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>272700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>229500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>313500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>237800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>265000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>255000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>258700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>249200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>243600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>205900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>158500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>165800</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>158300</v>
+      </c>
+      <c r="E58" s="3">
         <v>152700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>151000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>147200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>140700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>136700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>134900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>131300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>128500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>127500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>121100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>115900</v>
-      </c>
-      <c r="O58" s="3">
-        <v>2100</v>
       </c>
       <c r="P58" s="3">
         <v>2100</v>
       </c>
       <c r="Q58" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="R58" s="3">
         <v>1600</v>
       </c>
       <c r="S58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T58" s="3">
         <v>2100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1800</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
       <c r="AB58" s="3">
         <v>0</v>
       </c>
       <c r="AC58" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="AD58" s="3">
         <v>3500</v>
@@ -5983,474 +6116,489 @@
         <v>3500</v>
       </c>
       <c r="AN58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AO58" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>109300</v>
+      </c>
+      <c r="E59" s="3">
         <v>35200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>36200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>96700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>76400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>77500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>77400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>99500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>75800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>82500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>87500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>413800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>417200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>425500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>403300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>368000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>376100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>325500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>268700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>279300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>253700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>205100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>184900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>184100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>174100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>148400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>165400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>87300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>82900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>66800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>72600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>97100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>91500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>75300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>83800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>81700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1151400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1255200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1237800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1253500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1244200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1193000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1149200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1073600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1152000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1174400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1116200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1006500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1006800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1061400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1197300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1093300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1032000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1012000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>860200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>673000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>698800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>618900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>533700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>506500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>552500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>492400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>424600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>398300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>404300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>324200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>335300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>331100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>359300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>344200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>322400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>293200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>243700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1833200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1832700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1800900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1806300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1545800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1563100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1556900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1532600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1496700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1520300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1507100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1553300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>405600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>371900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>264200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>195700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>195800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>195900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>195400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>195500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>207200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>206800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>207000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>413300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>142600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>143300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>140500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>143300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>141800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>142500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>156800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>169800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>185600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>183900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>178300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>351200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>387200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>157600</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E62" s="3">
         <v>25500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>22500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1281800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1228800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1243700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1202000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1179700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1155300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1129000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1015500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>977000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>957200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>937600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>904800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>864800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>798100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>775100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>711800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>103700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>101500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>91600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>87400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>80300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>84600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>82300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>77800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>65900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6565,8 +6713,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6681,8 +6832,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6797,124 +6951,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3060500</v>
+      </c>
+      <c r="E66" s="3">
         <v>3158600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3116900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3146500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2880300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2821200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2771500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2677900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2731600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2752600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2665700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2606800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2694100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2662000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2705100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2491000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2407500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2363200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2184700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1884000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1883000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1782900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1678200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1824600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1560000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1433800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1340200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1253400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>649800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>568200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>583700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>588300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>625100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>612800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>583100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>722200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>696900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>479100</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6955,8 +7115,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7071,8 +7232,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7187,8 +7351,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7303,8 +7470,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7419,124 +7589,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1830900</v>
+      </c>
+      <c r="E72" s="3">
         <v>1791600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1734300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1671200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1622300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1574800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1523100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1466400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1416400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1379300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1313400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1241900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1170400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1101200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1025000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>943200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>872200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>822400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>747700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>664800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>589000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>531900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>463100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>431100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>394000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>358700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>317700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>274100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>243600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>225700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>199100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>159200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>119600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>71600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>48300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>27900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>16800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7651,8 +7827,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7767,8 +7946,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7883,124 +8065,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2408800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2362200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2294300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2221800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2170200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2111100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2046600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1980800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1931000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1885500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1809800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1728400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1657200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1582600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1494300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1402400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1323200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1264900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1179600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1080700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>997400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>931500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>850500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>809300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>764300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>723000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>670900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>620000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>584300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>563700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>534700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>487600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>442900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>388200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>361100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>146100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>134300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>341400</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8115,245 +8303,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46016</v>
+      </c>
+      <c r="E80" s="2">
         <v>45925</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45743</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45652</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45561</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45470</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45379</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45288</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45197</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45106</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45015</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44924</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44833</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44560</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44378</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44287</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44098</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44007</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43916</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43825</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43734</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43643</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43552</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43461</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43370</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43279</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43188</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43097</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43006</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42915</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42824</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42733</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E81" s="3">
         <v>57300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>63200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>48900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>47500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>51700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>56700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>50000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>37100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>65900</v>
-      </c>
-      <c r="M81" s="3">
-        <v>71500</v>
       </c>
       <c r="N81" s="3">
         <v>71500</v>
       </c>
       <c r="O81" s="3">
+        <v>71500</v>
+      </c>
+      <c r="P81" s="3">
         <v>69200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>76200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>81800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>71000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>49900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>74600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>82900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>75800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>57100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>68800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>32000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>37100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>35300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>41000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>43600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>30700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>17900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>26600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>39800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>31900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>48000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>23300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>20400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>11100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>16700</v>
       </c>
-      <c r="AN81" s="3" t="s">
+      <c r="AO81" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8394,124 +8591,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E83" s="3">
         <v>57900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>58400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>56400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>51400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>50900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>49700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>46400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>39200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>40100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>38000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>34600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>42300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>40100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>38000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>34600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>33700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>30400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>27700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>26400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>24400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>22900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>22300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>22100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>20700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>18400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>17700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>17200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>14900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>13400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>12100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>11500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>10400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>9600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>9100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>8900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>8300</v>
       </c>
-      <c r="AN83" s="3" t="s">
+      <c r="AO83" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8626,8 +8827,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8742,8 +8946,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8858,8 +9065,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8974,8 +9184,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9090,124 +9303,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>124100</v>
+      </c>
+      <c r="E89" s="3">
         <v>102500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>84100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>71200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>101400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>160300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>194000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>147500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>104600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>222300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>226400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>250300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>105100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>11200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-63600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>108300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>155600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>101000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>136500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>173000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>72000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>24700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>87400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>95100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>27000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>41900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>59800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>43300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>40600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>26300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>16400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>10400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>56100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>18500</v>
       </c>
-      <c r="AN89" s="3" t="s">
+      <c r="AO89" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9248,124 +9467,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-78900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-78000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-94100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-66700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-97500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-123700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-113900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-111700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-133900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-134500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-139800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-139400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-133800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-108500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-113400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-130000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-145600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-86200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-45900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-102800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-43700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-27600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-55000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-62800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-46500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-42000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-35600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-27800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-24100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-19800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AN91" s="3" t="s">
+      <c r="AO91" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9480,8 +9703,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9596,124 +9822,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-78900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-78000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-94100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-66700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-97500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-123700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-113900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-111700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-133900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-134700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-156900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-139400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-136500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-108500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-109200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-101400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-130000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-145800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-149600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-45900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-102800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-43700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-27600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-55000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-46500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-31600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-46000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-27800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-32600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-25700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-22400</v>
       </c>
-      <c r="AN94" s="3" t="s">
+      <c r="AO94" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9754,8 +9986,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9792,8 +10025,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9870,8 +10103,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9986,8 +10222,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10102,8 +10341,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10218,124 +10460,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>3100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-30100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-70300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-115600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>33400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>110600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>72400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>6000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-8800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>7400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-199900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>276600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>8100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>4400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-13800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-7700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>6300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>7900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>15300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-36300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>4000</v>
       </c>
-      <c r="AN100" s="3" t="s">
+      <c r="AO100" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10372,8 +10620,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10450,98 +10698,101 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>44800</v>
+      </c>
+      <c r="E102" s="3">
         <v>27600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>42700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>80600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>23000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-27200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>57500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-25700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-107600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-190600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-36000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>12000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>46300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>36600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>136700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-155500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>262900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-57100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>32700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>51000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>100</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
       <c r="AG102" s="3">
         <v>0</v>
       </c>
@@ -10552,18 +10803,21 @@
         <v>0</v>
       </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-100</v>
       </c>
-      <c r="AL102" s="3">
-        <v>0</v>
-      </c>
       <c r="AM102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="3">
         <v>100</v>
       </c>
-      <c r="AN102" s="3" t="s">
+      <c r="AO102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FND_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>FND</t>
   </si>
@@ -656,529 +656,542 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46107</v>
+      </c>
+      <c r="E7" s="2">
         <v>46016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45925</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45743</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45652</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45561</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45470</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45379</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45288</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45197</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45106</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45015</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44924</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44833</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44560</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44378</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44287</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44098</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44007</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43916</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43825</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43734</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43643</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43552</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43461</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43370</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43279</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43188</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43097</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43006</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42915</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42824</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42733</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1152300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1129700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1179500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1214200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1160700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1107400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1117900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1133100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1097300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1048100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1107800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1135900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1122100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1048100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1097800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1089800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1028700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>914300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>876600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>860100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>782500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>723700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>684800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>462400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>554900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>527000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>521100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>520300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>477100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>436700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>435900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>434300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>402900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>389500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>343900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>344000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>307300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>278300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>271300</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>629100</v>
+      </c>
+      <c r="E9" s="3">
         <v>623100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>652500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>666600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>641400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>619200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>625400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>635300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>620200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>599800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>633500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>650700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>646200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>612200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>650300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>653600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>620700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>559700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>511200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>494700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>445600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>416100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>390200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>265700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>318900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>297000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>307300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>302500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>275700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>255700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>257700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>256600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>237600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>227100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>201400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>201800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>181800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>163500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>160300</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>523200</v>
+      </c>
+      <c r="E10" s="3">
         <v>506600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>527100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>547600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>519300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>488200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>492500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>497900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>477100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>448400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>474300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>485200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>475800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>435900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>447500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>436200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>408000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>354600</v>
-      </c>
-      <c r="U10" s="3">
-        <v>365400</v>
       </c>
       <c r="V10" s="3">
         <v>365400</v>
       </c>
       <c r="W10" s="3">
+        <v>365400</v>
+      </c>
+      <c r="X10" s="3">
         <v>336900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>307600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>294600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>196700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>236000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>230000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>213800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>217800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>201400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>181000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>178200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>177700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>165300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>162400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>142500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>142200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>125500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>114800</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1220,8 +1233,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1339,8 +1353,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1458,22 +1475,25 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>-400</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1484,26 +1504,26 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>900</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>1400</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1511,35 +1531,35 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>1700</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1547,8 +1567,8 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1556,71 +1576,74 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK14" s="3">
         <v>0</v>
       </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>5400</v>
       </c>
-      <c r="AM14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AN14" s="3">
+      <c r="AN14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO14" s="3">
         <v>1700</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E15" s="3">
         <v>60700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>60500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>60000</v>
       </c>
       <c r="G15" s="3">
         <v>60000</v>
       </c>
       <c r="H15" s="3">
+        <v>60000</v>
+      </c>
+      <c r="I15" s="3">
         <v>59800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>57900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>58400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>56400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>54900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>50900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>49700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>46400</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1696,8 +1719,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,246 +1762,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1099900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1077700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1107500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1132300</v>
       </c>
-      <c r="G17" s="3">
-        <v>1096900</v>
-      </c>
       <c r="H17" s="3">
+        <v>1096500</v>
+      </c>
+      <c r="I17" s="3">
         <v>1048200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1051600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1061800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1037400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1001100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1023000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1040900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1025100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>953300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>996200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>983400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>934800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>853200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>793200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>763300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>686600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>655600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>606000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>440200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>508300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>484900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>489700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>474400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>437300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>413400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>401600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>397000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>366400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>357100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>315300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>315400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>284600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>260000</v>
       </c>
-      <c r="AO17" s="3" t="s">
+      <c r="AP17" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E18" s="3">
         <v>51900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>72000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>81900</v>
       </c>
-      <c r="G18" s="3">
-        <v>63900</v>
-      </c>
       <c r="H18" s="3">
+        <v>64200</v>
+      </c>
+      <c r="I18" s="3">
         <v>59200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>66300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>71300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>59900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>47100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>84800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>95000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>97000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>94800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>101600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>106400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>93900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>61100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>83400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>96800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>95900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>68100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>78800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>22200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>46600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>42100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>31400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>45900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>39800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>23300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>34300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>37300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>36500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>32400</v>
-      </c>
-      <c r="AK18" s="3">
-        <v>28600</v>
       </c>
       <c r="AL18" s="3">
         <v>28600</v>
       </c>
       <c r="AM18" s="3">
+        <v>28600</v>
+      </c>
+      <c r="AN18" s="3">
         <v>22700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>18300</v>
       </c>
-      <c r="AO18" s="3" t="s">
+      <c r="AP18" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2017,8 +2050,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2058,8 +2092,8 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -2077,11 +2111,11 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>900</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -2104,11 +2138,11 @@
         <v>0</v>
       </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
@@ -2133,487 +2167,502 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
-      <c r="AO20" s="3" t="s">
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>113700</v>
+      </c>
+      <c r="E21" s="3">
         <v>112600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>132600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>141900</v>
       </c>
-      <c r="G21" s="3">
-        <v>123800</v>
-      </c>
       <c r="H21" s="3">
+        <v>124200</v>
+      </c>
+      <c r="I21" s="3">
         <v>119000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>124200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>129700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>116300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>102000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>135700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>144700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>143300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>137100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>141800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>144400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>128600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>94800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>113800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>125400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>122400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>92400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>101700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>44400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>68800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>62800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>49800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>63600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>56900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>38300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>47600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>49300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>48000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>42800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>38200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>37800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>31600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>26600</v>
       </c>
-      <c r="AO21" s="3" t="s">
+      <c r="AP21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2600</v>
+        <v>3200</v>
       </c>
       <c r="E22" s="3">
         <v>2600</v>
       </c>
       <c r="F22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G22" s="3">
         <v>3000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>-2800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1200</v>
-      </c>
-      <c r="T22" s="3">
-        <v>1100</v>
       </c>
       <c r="U22" s="3">
         <v>1100</v>
       </c>
       <c r="V22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W22" s="3">
         <v>400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>2200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>2100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>2400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>2600</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>3400</v>
-      </c>
-      <c r="AM22" s="3">
-        <v>5400</v>
       </c>
       <c r="AN22" s="3">
         <v>5400</v>
       </c>
       <c r="AO22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AP22" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>51300</v>
+      </c>
+      <c r="E23" s="3">
         <v>51700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>71400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>80800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>62700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>59300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>66100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>70700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>57400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>45300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>83500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>92100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>90700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>89400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>98600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>104700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>92800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>60000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>82300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>97300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>94600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>65800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>76800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>19800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>44900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>40400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>29400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>43700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>36800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>20500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>32100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>35100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>34700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>30000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>26000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>25300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>17300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>12900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E24" s="3">
         <v>12400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>17600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>17600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>20600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>19100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>20200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>22500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>22900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>21900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>14300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>18800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>8000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-11600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>6100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>2700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>4900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>6100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-3800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2731,246 +2780,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E26" s="3">
         <v>39300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>57300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>63200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>48900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>47500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>51700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>56700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>50000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>37100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>65900</v>
-      </c>
-      <c r="N26" s="3">
-        <v>71500</v>
       </c>
       <c r="O26" s="3">
         <v>71500</v>
       </c>
       <c r="P26" s="3">
+        <v>71500</v>
+      </c>
+      <c r="Q26" s="3">
         <v>69200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>76200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>81800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>71000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>49900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>74600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>82900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>75800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>57100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>68800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>32000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>37100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>35300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>41000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>43600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>30700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>17300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>26000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>39800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>31900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>30100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>23300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>20400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>11100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>16700</v>
       </c>
-      <c r="AO26" s="3" t="s">
+      <c r="AP26" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E27" s="3">
         <v>39300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>57300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>63200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>48900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>47500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>51700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>56700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>50000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>37100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>65900</v>
-      </c>
-      <c r="N27" s="3">
-        <v>71500</v>
       </c>
       <c r="O27" s="3">
         <v>71500</v>
       </c>
       <c r="P27" s="3">
+        <v>71500</v>
+      </c>
+      <c r="Q27" s="3">
         <v>69200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>76200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>81800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>71000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>49900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>74600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>82900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>75800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>57100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>68800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>32000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>37100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>35300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>41000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>43600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>30700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>17300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>26000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>39800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>31900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>30100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>23300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>20400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>11100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>16700</v>
       </c>
-      <c r="AO27" s="3" t="s">
+      <c r="AP27" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3088,8 +3146,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3159,17 +3220,17 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3177,24 +3238,24 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>600</v>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG29" s="3">
         <v>600</v>
       </c>
       <c r="AH29" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>17800</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3207,8 +3268,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3326,8 +3390,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3445,8 +3512,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3486,8 +3556,8 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3505,11 +3575,11 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-900</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -3532,11 +3602,11 @@
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
@@ -3561,130 +3631,136 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
-      <c r="AO32" s="3" t="s">
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP32" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E33" s="3">
         <v>39300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>57300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>63200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>48900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>47500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>51700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>56700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>50000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>37100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>65900</v>
-      </c>
-      <c r="N33" s="3">
-        <v>71500</v>
       </c>
       <c r="O33" s="3">
         <v>71500</v>
       </c>
       <c r="P33" s="3">
+        <v>71500</v>
+      </c>
+      <c r="Q33" s="3">
         <v>69200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>76200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>81800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>71000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>49900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>74600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>82900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>75800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>57100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>68800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>32000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>37100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>35300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>41000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>43600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>30700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>17900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>26600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>39800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>31900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>48000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>23300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>20400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>11100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>16700</v>
       </c>
-      <c r="AO33" s="3" t="s">
+      <c r="AP33" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3802,251 +3878,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E35" s="3">
         <v>39300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>57300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>63200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>48900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>47500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>51700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>56700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>50000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>37100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>65900</v>
-      </c>
-      <c r="N35" s="3">
-        <v>71500</v>
       </c>
       <c r="O35" s="3">
         <v>71500</v>
       </c>
       <c r="P35" s="3">
+        <v>71500</v>
+      </c>
+      <c r="Q35" s="3">
         <v>69200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>76200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>81800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>71000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>49900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>74600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>82900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>75800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>57100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>68800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>32000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>37100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>35300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>41000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>43600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>30700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>17900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>26600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>39800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>31900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>48000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>23300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>20400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>11100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>16700</v>
       </c>
-      <c r="AO35" s="3" t="s">
+      <c r="AP35" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46107</v>
+      </c>
+      <c r="E38" s="2">
         <v>46016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45925</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45743</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45652</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45561</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45470</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45379</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45288</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45197</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45106</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45015</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44924</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44833</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44560</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44378</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44287</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44098</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44007</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43916</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43825</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43734</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43643</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43552</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43461</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43370</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43279</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43188</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43097</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43006</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42915</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42824</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42733</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4088,8 +4173,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4131,106 +4217,107 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>293600</v>
+      </c>
+      <c r="E41" s="3">
         <v>249300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>204500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>176900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>186900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>187700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>180800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>138100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>57400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>34400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>61600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>31800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>139400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>330100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>366100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>354100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>307800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>271100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>134400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>289900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>27000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>84100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>51500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>600</v>
-      </c>
-      <c r="AG41" s="3">
-        <v>500</v>
       </c>
       <c r="AH41" s="3">
         <v>500</v>
       </c>
       <c r="AI41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AJ41" s="3">
         <v>600</v>
@@ -4239,19 +4326,22 @@
         <v>600</v>
       </c>
       <c r="AL41" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AM41" s="3">
         <v>400</v>
       </c>
       <c r="AN41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AO41" s="3">
         <v>500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4280,11 +4370,11 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>1800</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4369,246 +4459,255 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>112600</v>
+      </c>
+      <c r="E43" s="3">
         <v>101300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>169600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>112800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>105500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>123200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>107700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>113400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>116800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>127400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>113900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>102300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>88000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>102100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>112400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>111700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>97800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>85000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>81500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>72800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>60000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>50400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>81000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>82100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>50600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>72200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>54500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>38500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>66100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>71900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>65900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>57200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>48000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>66500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>52600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>40600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>33400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>34500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>34800</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1149000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1133100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1164200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1211400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1189300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1132600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1046000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1037300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1032100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1106200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1105500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1172500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1181100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1292300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1320500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1344100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1149500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1008200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>833100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>683800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>607600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>654000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>598500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>594300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>588900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>581900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>484000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>446400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>437500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>471000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>403800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>432400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>426700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>428000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>395600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>367500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>316500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>293700</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>301600</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4648,205 +4747,211 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>53300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>56500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>49300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>43400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>40800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>49500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>42700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>40200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>28300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>23400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>19200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>21600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>20400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>21100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>27700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>23300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>15900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>16600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>12100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>8200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>7500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>7600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>9500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>7500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1605000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1527900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1594200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1553200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1531500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1492400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1388900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1342200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1256100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1316600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1336100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1335500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1328500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1457500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1497100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1511300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1322500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1273300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1294200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1165400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1061900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1040500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>974000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>830000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>951000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>701500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>643700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>564000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>527400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>559500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>486800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>502300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>486400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>503200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>456300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>416100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>359900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>336200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>343800</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4862,11 +4967,11 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
@@ -4886,8 +4991,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4964,189 +5069,195 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3498100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3473900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3467400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3407800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3392700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3117800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3110600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3043100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2969100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2912500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2869100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2701200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2576500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2463700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2321500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2263500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2144500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2032800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1918300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1782400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1558800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1495700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1396900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1354900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1338600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1278500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1169000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1102700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>998000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>328400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>300300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>271500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>245400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>221000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>200400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>183600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>163800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>150500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>135500</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>403600</v>
+      </c>
+      <c r="E49" s="3">
         <v>404500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>405400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>406300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>407200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>408100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>409100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>410000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>410900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>411800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>412700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>414600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>407100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>407800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>406300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>407100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>407300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>407400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>408200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>408900</v>
-      </c>
-      <c r="W49" s="3">
-        <v>336700</v>
       </c>
       <c r="X49" s="3">
         <v>336700</v>
@@ -5164,7 +5275,7 @@
         <v>336700</v>
       </c>
       <c r="AC49" s="3">
-        <v>336800</v>
+        <v>336700</v>
       </c>
       <c r="AD49" s="3">
         <v>336800</v>
@@ -5202,8 +5313,11 @@
       <c r="AO49" s="3">
         <v>336800</v>
       </c>
+      <c r="AP49" s="3">
+        <v>336800</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5321,8 +5435,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5440,127 +5557,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E52" s="3">
         <v>43000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>35300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>22200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>19800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>17600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>19200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>17100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>11200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>7800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>7000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>7400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>7700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>7800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>7600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5678,127 +5801,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5576300</v>
+      </c>
+      <c r="E54" s="3">
         <v>5469400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5520800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5411200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5368300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5050500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4932200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4818100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4658700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4662600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4638100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4475500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4335200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4351200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4244700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4199400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3893400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3730700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3628100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3364300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2964700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2880400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2714400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2528700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2633900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2324300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2156900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2011100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1873400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1234100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1131900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1118400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1075900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1068000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1000900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>944200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>868400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>831200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>820400</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5840,8 +5969,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5883,210 +6013,214 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>735400</v>
+      </c>
+      <c r="E57" s="3">
         <v>683700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>724600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>777100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>814400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>794900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>737800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>698700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>641200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>679300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>706300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>664700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>572500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>590900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>642100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>770200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>688500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>661900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>634300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>529200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>402100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>417900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>362500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>326000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>319800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>368500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>318400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>272700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>229500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>313500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>237800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>265000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>255000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>258700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>249200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>243600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>205900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>158500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>165800</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>356600</v>
+      </c>
+      <c r="E58" s="3">
         <v>158300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>152700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>151000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>147200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>140700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>136700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>134900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>131300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>128500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>127500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>121100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>115900</v>
-      </c>
-      <c r="P58" s="3">
-        <v>2100</v>
       </c>
       <c r="Q58" s="3">
         <v>2100</v>
       </c>
       <c r="R58" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="S58" s="3">
         <v>1600</v>
       </c>
       <c r="T58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="U58" s="3">
         <v>2100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1800</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
       <c r="AC58" s="3">
         <v>0</v>
       </c>
       <c r="AD58" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="3">
         <v>3500</v>
@@ -6119,486 +6253,501 @@
         <v>3500</v>
       </c>
       <c r="AO58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AP58" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E59" s="3">
         <v>109300</v>
       </c>
-      <c r="E59" s="3">
-        <v>35200</v>
-      </c>
       <c r="F59" s="3">
+        <v>82200</v>
+      </c>
+      <c r="G59" s="3">
         <v>36200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>96700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>76400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>77500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>77400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>99500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>75800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>82500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>87500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>413800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>417200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>425500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>403300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>368000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>376100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>325500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>268700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>279300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>253700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>205100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>184900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>184100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>174100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>148400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>165400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>87300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>82900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>66800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>72600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>97100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>91500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>75300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>83800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>81700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1395100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1151400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1255200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1237800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1253500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1244200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1193000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1149200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1073600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1152000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1174400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1116200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1006500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1006800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1061400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1197300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1093300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1032000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1012000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>860200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>673000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>698800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>618900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>533700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>506500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>552500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>492400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>424600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>398300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>404300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>324200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>335300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>331100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>359300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>344200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>322400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>293200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>243700</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1650000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1833200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1832700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1800900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1806300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1545800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1563100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1556900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1532600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1496700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1520300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1507100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1553300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>405600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>371900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>264200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>195700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>195800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>195900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>195400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>195500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>207200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>206800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>207000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>413300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>142600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>143300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>140500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>143300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>141800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>142500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>156800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>169800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>185600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>183900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>178300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>351200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>387200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>157600</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E62" s="3">
         <v>26500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>25500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1281800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1228800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1243700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1202000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1179700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1155300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1129000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1015500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>977000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>957200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>937600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>904800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>864800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>798100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>775100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>711800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>103700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>101500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>91600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>87400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>80300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>84600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>82300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>77800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>65900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6716,8 +6865,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6835,8 +6987,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6954,127 +7109,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3119600</v>
+      </c>
+      <c r="E66" s="3">
         <v>3060500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3158600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3116900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3146500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2880300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2821200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2771500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2677900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2731600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2752600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2665700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2606800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2694100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2662000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2705100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2491000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2407500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2363200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2184700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1884000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1883000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1782900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1678200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1824600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1560000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1433800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1340200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1253400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>649800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>568200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>583700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>588300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>625100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>612800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>583100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>722200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>696900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>479100</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7116,8 +7277,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7235,8 +7397,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7354,8 +7519,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7473,8 +7641,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7592,127 +7763,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1870600</v>
+      </c>
+      <c r="E72" s="3">
         <v>1830900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1791600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1734300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1671200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1622300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1574800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1523100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1466400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1416400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1379300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1313400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1241900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1170400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1101200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1025000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>943200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>872200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>822400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>747700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>664800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>589000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>531900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>463100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>431100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>394000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>358700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>317700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>274100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>243600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>225700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>199100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>159200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>119600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>71600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>48300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>27900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>16800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>74300</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7830,8 +8007,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7949,8 +8129,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8068,127 +8251,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2456700</v>
+      </c>
+      <c r="E76" s="3">
         <v>2408800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2362200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2294300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2221800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2170200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2111100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2046600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1980800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1931000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1885500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1809800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1728400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1657200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1582600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1494300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1402400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1323200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1264900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1179600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1080700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>997400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>931500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>850500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>809300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>764300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>723000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>670900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>620000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>584300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>563700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>534700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>487600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>442900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>388200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>361100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>146100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>134300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>341400</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8306,251 +8495,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46107</v>
+      </c>
+      <c r="E80" s="2">
         <v>46016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45925</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45743</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45652</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45561</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45470</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45379</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45288</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45197</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45106</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45015</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44924</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44833</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44560</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44378</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44287</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44098</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44007</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43916</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43825</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43734</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43643</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43552</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43461</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43370</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43279</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43188</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43097</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43006</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42915</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42824</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42733</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E81" s="3">
         <v>39300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>57300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>63200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>48900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>47500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>51700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>56700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>50000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>37100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>65900</v>
-      </c>
-      <c r="N81" s="3">
-        <v>71500</v>
       </c>
       <c r="O81" s="3">
         <v>71500</v>
       </c>
       <c r="P81" s="3">
+        <v>71500</v>
+      </c>
+      <c r="Q81" s="3">
         <v>69200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>76200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>81800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>71000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>49900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>74600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>82900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>75800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>57100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>68800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>32000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>37100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>35300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>41000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>43600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>30700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>17900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>26600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>39800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>31900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>48000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>23300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>20400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>11100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>16700</v>
       </c>
-      <c r="AO81" s="3" t="s">
+      <c r="AP81" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8592,127 +8790,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E83" s="3">
         <v>56100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>57900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>58400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>56400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>51400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>50900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>49700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>46400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>39200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>40100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>38000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>34600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>42300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>40100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>38000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>34600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>33700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>30400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>27700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>26400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>24400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>22900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>22300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>22100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>20700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>18400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>17700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>17200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>14900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>13400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>12100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>11500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>10400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>9600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>9100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>8900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>8300</v>
       </c>
-      <c r="AO83" s="3" t="s">
+      <c r="AP83" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8830,8 +9032,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8949,8 +9154,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9068,8 +9276,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9187,8 +9398,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9306,127 +9520,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>109200</v>
+      </c>
+      <c r="E89" s="3">
         <v>124100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>102500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>84100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>71200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>101400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>160300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>194000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>147500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>104600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>222300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>226400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>250300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>105100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>11200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-63600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>108300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>155600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>101000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>136500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>173000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>72000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>24700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>87400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>95100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>27000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>41900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>59800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>43300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>40600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>26300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>16400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>10400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>56100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>18500</v>
       </c>
-      <c r="AO89" s="3" t="s">
+      <c r="AP89" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9468,127 +9688,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-63400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-78900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-78000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-94100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-66700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-97500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-123700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-113900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-111700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-133900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-134500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-139800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-139400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-133800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-108500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-113400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-130000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-145600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-86200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-45900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-102800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-43700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-27600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-55000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-62800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-46500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-42000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-35600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-27800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-24100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-19800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AO91" s="3" t="s">
+      <c r="AP91" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9706,8 +9930,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9825,127 +10052,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-63400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-78900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-78000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-94100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-66700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-97500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-123700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-113900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-111700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-133900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-134700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-156900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-139400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-136500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-108500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-109200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-101400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-130000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-145800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-149600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-45900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-102800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-43700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-27600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-55000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-62800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-46500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-31600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-46000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-27800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-32600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-25700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-22400</v>
       </c>
-      <c r="AO94" s="3" t="s">
+      <c r="AP94" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9987,8 +10220,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10028,8 +10262,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10106,8 +10340,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10225,8 +10462,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10344,8 +10584,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10463,127 +10706,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-30100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-70300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-115600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>33400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>110600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>72400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-8800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>7400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-199900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>276600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>8100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>4400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-13800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-7700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>6300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>7900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>15300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-36300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>4000</v>
       </c>
-      <c r="AO100" s="3" t="s">
+      <c r="AP100" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10623,8 +10872,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10701,101 +10950,104 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E102" s="3">
         <v>44800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>27600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-10100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>42700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>80600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>23000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-27200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>57500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-25700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-107600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-190600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-36000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>12000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>46300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>36600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>136700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-155500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>262900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-57100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>32700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>51000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>100</v>
       </c>
-      <c r="AG102" s="3">
-        <v>0</v>
-      </c>
       <c r="AH102" s="3">
         <v>0</v>
       </c>
@@ -10806,18 +11058,21 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3">
         <v>200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-100</v>
       </c>
-      <c r="AM102" s="3">
-        <v>0</v>
-      </c>
       <c r="AN102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="3">
         <v>100</v>
       </c>
-      <c r="AO102" s="3" t="s">
+      <c r="AP102" s="3" t="s">
         <v>8</v>
       </c>
     </row>
